--- a/Assets/GameData/database.xlsx
+++ b/Assets/GameData/database.xlsx
@@ -116,6 +116,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFDEE0E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD5F6F2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFD5F6F2"/>
         <bgColor/>
       </patternFill>
@@ -152,12 +164,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDEE0E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFF258"/>
         <bgColor/>
       </patternFill>
@@ -176,25 +182,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD5F6F2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFF258"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD5F6F2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD5F6F2"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -213,6 +201,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF8F959E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD5F6F2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD5F6F2"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -403,44 +403,44 @@
     <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0">
       <alignment vertical="center" wrapText="true"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0">
+    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="2" fillId="2" fontId="1" numFmtId="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="true"/>
+    </xf>
+    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="3" fillId="3" fontId="2" numFmtId="0" xfId="0">
+      <alignment vertical="center" wrapText="true"/>
+    </xf>
+    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="4" fillId="4" fontId="1" numFmtId="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="true"/>
+    </xf>
+    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="5" fillId="5" fontId="1" numFmtId="0" xfId="0">
+      <alignment vertical="center" wrapText="true"/>
+    </xf>
+    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="6" fillId="6" fontId="2" numFmtId="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="true"/>
+    </xf>
+    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="7" fillId="7" fontId="3" numFmtId="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="true"/>
+    </xf>
+    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="8" fillId="8" fontId="1" numFmtId="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="true"/>
+    </xf>
+    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="9" fillId="9" fontId="1" numFmtId="0" xfId="0">
+      <alignment vertical="center" wrapText="true"/>
+    </xf>
+    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="10" fillId="10" fontId="2" numFmtId="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="true"/>
+    </xf>
+    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="11" fillId="11" fontId="1" numFmtId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="3" fillId="2" fontId="2" numFmtId="0" xfId="0">
-      <alignment vertical="center" wrapText="true"/>
-    </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="4" fillId="3" fontId="1" numFmtId="0" xfId="0">
-      <alignment vertical="center" wrapText="true"/>
-    </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="5" fillId="4" fontId="1" numFmtId="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="true"/>
-    </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="6" fillId="5" fontId="2" numFmtId="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="true"/>
-    </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="7" fillId="6" fontId="1" numFmtId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="8" fillId="7" fontId="1" numFmtId="0" xfId="0">
-      <alignment vertical="center" wrapText="true"/>
-    </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="9" fillId="8" fontId="1" numFmtId="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="true"/>
-    </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="10" fillId="9" fontId="2" numFmtId="0" xfId="0">
+    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="12" fillId="12" fontId="1" numFmtId="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="11" fillId="10" fontId="1" numFmtId="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="true"/>
-    </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="12" fillId="11" fontId="1" numFmtId="0" xfId="0">
+    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="13" fillId="13" fontId="2" numFmtId="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="13" fillId="12" fontId="2" numFmtId="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="true"/>
-    </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="14" fillId="13" fontId="3" numFmtId="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="true"/>
+    <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="14" fillId="0" fontId="1" numFmtId="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
     <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="15" fillId="0" fontId="2" numFmtId="0" xfId="0">
       <alignment vertical="center"/>
@@ -452,22 +452,22 @@
       <alignment vertical="center" wrapText="true"/>
     </xf>
     <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="18" fillId="16" fontId="1" numFmtId="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment vertical="center"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="19" fillId="17" fontId="2" numFmtId="0" xfId="0">
+    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="19" fillId="17" fontId="1" numFmtId="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="20" fillId="18" fontId="2" numFmtId="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="true"/>
-    </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="21" fillId="19" fontId="1" numFmtId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="22" fillId="20" fontId="2" numFmtId="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="23" fillId="21" fontId="1" numFmtId="0" xfId="0">
+    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="21" fillId="19" fontId="2" numFmtId="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="22" fillId="20" fontId="1" numFmtId="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="23" fillId="21" fontId="2" numFmtId="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="true"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -815,252 +815,254 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="str">
+      <c r="A1" s="8" t="str">
         <v>CharacterId</v>
       </c>
-      <c r="B1" s="9" t="str">
+      <c r="B1" s="8" t="str">
         <v>Name</v>
       </c>
-      <c r="C1" s="9" t="str">
+      <c r="C1" s="8" t="str">
         <v>race</v>
       </c>
-      <c r="D1" s="11" t="str">
+      <c r="D1" s="4" t="str">
         <v>feature</v>
       </c>
-      <c r="E1" s="9" t="str">
+      <c r="E1" s="8" t="str">
         <v>Desc</v>
       </c>
-      <c r="F1" s="9" t="str">
+      <c r="F1" s="8" t="str">
         <v>Planet</v>
       </c>
-      <c r="G1" s="11" t="str">
-        <v>Comment</v>
-      </c>
-      <c r="H1" s="9" t="str">
+      <c r="G1" s="8" t="str">
+        <v>PlanetOption</v>
+      </c>
+      <c r="H1" s="8" t="str">
         <v>Items</v>
       </c>
-      <c r="I1" s="8" t="str">
+      <c r="I1" s="9" t="str">
         <v>Question1</v>
       </c>
-      <c r="J1" s="8"/>
-      <c r="K1" s="8" t="str">
+      <c r="J1" s="9"/>
+      <c r="K1" s="9" t="str">
         <v>Answer1</v>
       </c>
-      <c r="L1" s="8" t="str">
+      <c r="L1" s="9" t="str">
         <v>Question2</v>
       </c>
-      <c r="M1" s="8"/>
-      <c r="N1" s="8" t="str">
+      <c r="M1" s="9"/>
+      <c r="N1" s="9" t="str">
         <v>Answer2</v>
       </c>
-      <c r="O1" s="8" t="str">
+      <c r="O1" s="9" t="str">
         <v>Question3</v>
       </c>
-      <c r="P1" s="8"/>
-      <c r="Q1" s="8" t="str">
+      <c r="P1" s="9"/>
+      <c r="Q1" s="9" t="str">
         <v>Answer3</v>
       </c>
-      <c r="R1" s="8" t="str">
+      <c r="R1" s="9" t="str">
         <v>glitter1</v>
       </c>
-      <c r="S1" s="8" t="str">
+      <c r="S1" s="9" t="str">
         <v>glitter2</v>
       </c>
-      <c r="T1" s="8" t="str">
+      <c r="T1" s="9" t="str">
         <v>glitter3</v>
       </c>
-      <c r="U1" s="13" t="str">
+      <c r="U1" s="10" t="str">
         <v>Profile_picture</v>
       </c>
-      <c r="V1" s="13" t="str">
+      <c r="V1" s="10" t="str">
         <v>Full_appearance</v>
       </c>
-      <c r="W1" s="13" t="str">
+      <c r="W1" s="10" t="str">
         <v>Full_X</v>
       </c>
-      <c r="X1" s="8"/>
-      <c r="Y1" s="8"/>
-      <c r="Z1" s="8"/>
-      <c r="AA1" s="8"/>
-      <c r="AB1" s="8"/>
-      <c r="AC1" s="8"/>
-      <c r="AD1" s="8"/>
-      <c r="AE1" s="8"/>
-      <c r="AF1" s="8"/>
+      <c r="X1" s="9"/>
+      <c r="Y1" s="9"/>
+      <c r="Z1" s="9"/>
+      <c r="AA1" s="9"/>
+      <c r="AB1" s="9"/>
+      <c r="AC1" s="9"/>
+      <c r="AD1" s="9"/>
+      <c r="AE1" s="9"/>
+      <c r="AF1" s="9"/>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="str">
+      <c r="A2" s="8" t="str">
         <v>int</v>
       </c>
-      <c r="B2" s="9" t="str">
+      <c r="B2" s="8" t="str">
         <v>string</v>
       </c>
-      <c r="C2" s="9" t="str">
+      <c r="C2" s="8" t="str">
         <v>string</v>
       </c>
-      <c r="D2" s="11" t="str">
+      <c r="D2" s="4" t="str">
         <v>string</v>
       </c>
-      <c r="E2" s="9" t="str">
+      <c r="E2" s="8" t="str">
         <v>string</v>
       </c>
-      <c r="F2" s="9" t="str">
+      <c r="F2" s="8" t="str">
         <v>string</v>
       </c>
-      <c r="G2" s="11" t="str">
+      <c r="G2" s="8" t="str">
         <v>string</v>
       </c>
-      <c r="H2" s="9" t="str">
+      <c r="H2" s="8" t="str">
         <v>string</v>
       </c>
-      <c r="I2" s="8" t="str">
+      <c r="I2" s="9" t="str">
         <v>string</v>
       </c>
-      <c r="J2" s="8"/>
-      <c r="K2" s="8" t="str">
+      <c r="J2" s="9"/>
+      <c r="K2" s="9" t="str">
         <v>string</v>
       </c>
-      <c r="L2" s="8" t="str">
+      <c r="L2" s="9" t="str">
         <v>string</v>
       </c>
-      <c r="M2" s="8"/>
-      <c r="N2" s="8" t="str">
+      <c r="M2" s="9"/>
+      <c r="N2" s="9" t="str">
         <v>string</v>
       </c>
-      <c r="O2" s="8" t="str">
+      <c r="O2" s="9" t="str">
         <v>string</v>
       </c>
-      <c r="P2" s="8"/>
-      <c r="Q2" s="8" t="str">
+      <c r="P2" s="9"/>
+      <c r="Q2" s="9" t="str">
         <v>string</v>
       </c>
-      <c r="R2" s="8" t="str">
+      <c r="R2" s="9" t="str">
         <v>string</v>
       </c>
-      <c r="S2" s="8" t="str">
+      <c r="S2" s="9" t="str">
         <v>string</v>
       </c>
-      <c r="T2" s="8" t="str">
+      <c r="T2" s="9" t="str">
         <v>string</v>
       </c>
-      <c r="U2" s="13" t="str">
+      <c r="U2" s="10" t="str">
         <v>string</v>
       </c>
-      <c r="V2" s="13" t="str">
+      <c r="V2" s="10" t="str">
         <v>string</v>
       </c>
-      <c r="W2" s="13" t="str">
+      <c r="W2" s="10" t="str">
         <v>string</v>
       </c>
-      <c r="X2" s="8"/>
-      <c r="Y2" s="8"/>
-      <c r="Z2" s="8"/>
-      <c r="AA2" s="8"/>
-      <c r="AB2" s="8"/>
-      <c r="AC2" s="8"/>
-      <c r="AD2" s="8"/>
-      <c r="AE2" s="8"/>
-      <c r="AF2" s="8"/>
+      <c r="X2" s="9"/>
+      <c r="Y2" s="9"/>
+      <c r="Z2" s="9"/>
+      <c r="AA2" s="9"/>
+      <c r="AB2" s="9"/>
+      <c r="AC2" s="9"/>
+      <c r="AD2" s="9"/>
+      <c r="AE2" s="9"/>
+      <c r="AF2" s="9"/>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="str">
+      <c r="A3" s="8" t="str">
         <v>唯一id</v>
       </c>
       <c r="B3" s="12" t="str" xml:space="preserve">
         <v> 角色的姓名</v>
       </c>
-      <c r="C3" s="9" t="str">
+      <c r="C3" s="8" t="str">
         <v>种族</v>
       </c>
-      <c r="D3" s="11" t="str">
+      <c r="D3" s="4" t="str">
         <v>特点</v>
       </c>
-      <c r="E3" s="9" t="str">
+      <c r="E3" s="8" t="str">
         <v>描述</v>
       </c>
-      <c r="F3" s="9" t="str">
+      <c r="F3" s="8" t="str">
         <v>星球</v>
       </c>
-      <c r="G3" s="11" t="str">
-        <v>备注</v>
-      </c>
-      <c r="H3" s="9" t="str">
+      <c r="G3" s="8" t="str">
+        <v>备选星球</v>
+      </c>
+      <c r="H3" s="8" t="str">
         <v>小动物携带的道具ID用“|”分割</v>
       </c>
-      <c r="I3" s="7" t="str">
+      <c r="I3" s="11" t="str">
         <v>第一个问题</v>
       </c>
-      <c r="J3" s="7" t="str">
+      <c r="J3" s="11" t="str">
         <v>关键字1</v>
       </c>
-      <c r="K3" s="7" t="str">
+      <c r="K3" s="11" t="str">
         <v>回答一对应的prefab资源的名字</v>
       </c>
-      <c r="L3" s="7" t="str">
+      <c r="L3" s="11" t="str">
         <v>第二个问题</v>
       </c>
-      <c r="M3" s="7" t="str">
+      <c r="M3" s="11" t="str">
         <v>关键字2</v>
       </c>
-      <c r="N3" s="7" t="str">
+      <c r="N3" s="11" t="str">
         <v>回答二对应的prefab资源的名字</v>
       </c>
-      <c r="O3" s="7" t="str">
+      <c r="O3" s="11" t="str">
         <v>第三个问题</v>
       </c>
-      <c r="P3" s="7" t="str">
+      <c r="P3" s="11" t="str">
         <v>关键字3</v>
       </c>
-      <c r="Q3" s="7" t="str">
+      <c r="Q3" s="11" t="str">
         <v>回答三对应的prefab资源的名字</v>
       </c>
-      <c r="R3" s="7" t="str">
+      <c r="R3" s="11" t="str">
         <v>闪光点1描述</v>
       </c>
-      <c r="S3" s="7" t="str">
+      <c r="S3" s="11" t="str">
         <v>闪光点2描述</v>
       </c>
-      <c r="T3" s="8" t="str">
+      <c r="T3" s="9" t="str">
         <v>闪光点3描述</v>
       </c>
-      <c r="U3" s="10" t="str">
+      <c r="U3" s="13" t="str">
         <v>profile头像</v>
       </c>
-      <c r="V3" s="10" t="str">
+      <c r="V3" s="13" t="str">
         <v>全身外貌滤波器</v>
       </c>
-      <c r="W3" s="10" t="str">
+      <c r="W3" s="13" t="str">
         <v>全身x光滤波器</v>
       </c>
-      <c r="X3" s="8"/>
-      <c r="Y3" s="8"/>
-      <c r="Z3" s="8"/>
-      <c r="AA3" s="8"/>
-      <c r="AB3" s="8"/>
-      <c r="AC3" s="8"/>
-      <c r="AD3" s="8"/>
-      <c r="AE3" s="8"/>
-      <c r="AF3" s="8"/>
+      <c r="X3" s="9"/>
+      <c r="Y3" s="9"/>
+      <c r="Z3" s="9"/>
+      <c r="AA3" s="9"/>
+      <c r="AB3" s="9"/>
+      <c r="AC3" s="9"/>
+      <c r="AD3" s="9"/>
+      <c r="AE3" s="9"/>
+      <c r="AF3" s="9"/>
     </row>
     <row r="4">
-      <c r="A4" s="5">
+      <c r="A4" s="2">
         <v>1</v>
       </c>
       <c r="B4" s="3" t="str">
         <v>Groot</v>
       </c>
-      <c r="C4" s="5" t="str">
+      <c r="C4" s="2" t="str">
         <v>Sprout</v>
       </c>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5" t="str">
+      <c r="D4" s="4" t="str">
+        <v>A：人畜无害</v>
+      </c>
+      <c r="E4" s="2" t="str">
         <v>Plant-like sprouts grow on its antennae. Its jagged, tooth-like body serves as perfect camouflage to evade natural enemies.</v>
       </c>
-      <c r="F4" s="5">
+      <c r="F4" s="2">
         <v>1</v>
       </c>
-      <c r="G4" s="5" t="str">
-        <v>A：人畜无害</v>
+      <c r="G4" s="6" t="str">
+        <v>7|8|1</v>
       </c>
       <c r="H4" s="6" t="str">
         <v>1|2</v>
@@ -1080,13 +1082,13 @@
       <c r="Q4" s="3" t="str">
         <v>Groot_prefab_3</v>
       </c>
-      <c r="R4" s="4" t="str">
+      <c r="R4" s="5" t="str">
         <v>The pale green sprout is, in truth, its true form.</v>
       </c>
-      <c r="S4" s="4" t="str">
+      <c r="S4" s="5" t="str">
         <v>The dark markings aren't actually eyes.</v>
       </c>
-      <c r="T4" s="4" t="str">
+      <c r="T4" s="5" t="str">
         <v>Its soft little feet are enough to carry it in quick hops and light sprints.
 </v>
       </c>
@@ -1110,24 +1112,26 @@
       <c r="AF4" s="1"/>
     </row>
     <row r="5">
-      <c r="A5" s="5">
+      <c r="A5" s="2">
         <v>2</v>
       </c>
       <c r="B5" s="3" t="str">
         <v>BuBoom</v>
       </c>
-      <c r="C5" s="5" t="str">
+      <c r="C5" s="2" t="str">
         <v>Inorganic</v>
       </c>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5" t="str">
+      <c r="D5" s="4" t="str">
+        <v>B：轻微迷惑性的危险</v>
+      </c>
+      <c r="E5" s="2" t="str">
         <v>A Balloonian who changes color according to its emotional state.</v>
       </c>
-      <c r="F5" s="5">
+      <c r="F5" s="2">
         <v>2</v>
       </c>
-      <c r="G5" s="5" t="str">
-        <v>B：轻微迷惑性的危险</v>
+      <c r="G5" s="6" t="str">
+        <v>2|6|10</v>
       </c>
       <c r="H5" s="6">
         <v>3</v>
@@ -1147,14 +1151,14 @@
       <c r="Q5" s="3" t="str">
         <v>BuBoom_prefab_3</v>
       </c>
-      <c r="R5" s="4" t="str" xml:space="preserve">
+      <c r="R5" s="5" t="str" xml:space="preserve">
         <v>Years of overwork have left its scalp smooth, with only a few hairs still holding the line.
  </v>
       </c>
-      <c r="S5" s="4" t="str">
+      <c r="S5" s="5" t="str">
         <v>Multiple joints are worn and damaged.</v>
       </c>
-      <c r="T5" s="4" t="str">
+      <c r="T5" s="5" t="str">
         <v>A special model from Tonis Star Industries—no repairs, only replacements.</v>
       </c>
       <c r="U5" s="3" t="str">
@@ -1177,26 +1181,28 @@
       <c r="AF5" s="1"/>
     </row>
     <row r="6">
-      <c r="A6" s="5">
+      <c r="A6" s="2">
         <v>3</v>
       </c>
       <c r="B6" s="3" t="str">
         <v>Bank</v>
       </c>
-      <c r="C6" s="5" t="str">
+      <c r="C6" s="2" t="str">
         <v>Urban Legend</v>
       </c>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5" t="str">
+      <c r="D6" s="4" t="str">
+        <v>C：看上去有攻击性，实际很危险</v>
+      </c>
+      <c r="E6" s="2" t="str">
         <v>An eerie Mothman-like entity born from urban legends on Fajnara. In truth, it belongs to the dominant species of the planet Frattwizz.</v>
       </c>
-      <c r="F6" s="5">
+      <c r="F6" s="2">
         <v>3</v>
       </c>
-      <c r="G6" s="5" t="str">
-        <v>C：看上去有攻击性，实际很危险</v>
-      </c>
-      <c r="H6" s="14" t="str">
+      <c r="G6" s="6" t="str">
+        <v>5|3|9</v>
+      </c>
+      <c r="H6" s="7" t="str">
         <v>4|5|6</v>
       </c>
       <c r="I6" s="1"/>
@@ -1214,14 +1220,14 @@
       <c r="Q6" s="3" t="str">
         <v>Bank_prefab_3</v>
       </c>
-      <c r="R6" s="4" t="str">
+      <c r="R6" s="5" t="str">
         <v>Glints beneath the fluff resemble eye-like reflections.
 </v>
       </c>
-      <c r="S6" s="4" t="str">
+      <c r="S6" s="5" t="str">
         <v>A ring of red marks its ankles—left by long-term restraints.</v>
       </c>
-      <c r="T6" s="4" t="str">
+      <c r="T6" s="5" t="str">
         <v>Bold, deep eye-like patterns signal its status as a dominant specimen.</v>
       </c>
       <c r="U6" s="3" t="str">
@@ -1244,24 +1250,26 @@
       <c r="AF6" s="1"/>
     </row>
     <row r="7">
-      <c r="A7" s="5">
+      <c r="A7" s="2">
         <v>4</v>
       </c>
       <c r="B7" s="3" t="str">
         <v>G-007</v>
       </c>
-      <c r="C7" s="5" t="str">
+      <c r="C7" s="2" t="str">
         <v>Ferro</v>
       </c>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5" t="str">
+      <c r="D7" s="4" t="str">
+        <v>D：看起来有攻击性，但是善良的</v>
+      </c>
+      <c r="E7" s="2" t="str">
         <v>A satellite signal detection model. It was once the most common robot type used in interstellar exploration.</v>
       </c>
-      <c r="F7" s="5">
+      <c r="F7" s="2">
         <v>4</v>
       </c>
-      <c r="G7" s="5" t="str">
-        <v>D：看起来有攻击性，但是善良的</v>
+      <c r="G7" s="6" t="str">
+        <v>2|4|7</v>
       </c>
       <c r="H7" s="6" t="str">
         <v>7|8</v>
@@ -1281,14 +1289,14 @@
       <c r="Q7" s="3" t="str">
         <v>G-007_prefab_3</v>
       </c>
-      <c r="R7" s="4" t="str">
+      <c r="R7" s="5" t="str">
         <v>The long-disabled cannon mouth still lets out the occasional dull boom, as if insisting it exists.
 </v>
       </c>
-      <c r="S7" s="4" t="str">
+      <c r="S7" s="5" t="str">
         <v>The stabilizing screws are gone without a trace, yet it still stands.</v>
       </c>
-      <c r="T7" s="4" t="str">
+      <c r="T7" s="5" t="str">
         <v>At its core, a red light continues to glow…</v>
       </c>
       <c r="U7" s="3" t="str">
@@ -1311,26 +1319,28 @@
       <c r="AF7" s="1"/>
     </row>
     <row r="8">
-      <c r="A8" s="5">
+      <c r="A8" s="2">
         <v>5</v>
       </c>
       <c r="B8" s="3" t="str">
         <v>Ivy-chan</v>
       </c>
-      <c r="C8" s="5" t="str">
+      <c r="C8" s="2" t="str">
         <v>Beast</v>
       </c>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5" t="str">
+      <c r="D8" s="4" t="str">
+        <v>E：看不出来，白切黑</v>
+      </c>
+      <c r="E8" s="2" t="str">
         <v>A cute little vine critter that loves snuggling up to furry creatures and climbing all over them.</v>
       </c>
-      <c r="F8" s="5">
+      <c r="F8" s="2">
         <v>5</v>
       </c>
-      <c r="G8" s="5" t="str">
-        <v>E：看不出来，白切黑</v>
-      </c>
-      <c r="H8" s="14" t="str">
+      <c r="G8" s="6" t="str">
+        <v>8|10|5</v>
+      </c>
+      <c r="H8" s="7" t="str">
         <v>9|10|11|12</v>
       </c>
       <c r="I8" s="1"/>
@@ -1348,14 +1358,14 @@
       <c r="Q8" s="3" t="str">
         <v>Ivy-chan_prefab_3</v>
       </c>
-      <c r="R8" s="4" t="str">
+      <c r="R8" s="5" t="str">
         <v>What look like patterns across its body… are actually tiny faces?
 </v>
       </c>
-      <c r="S8" s="4" t="str">
+      <c r="S8" s="5" t="str">
         <v>Thin brown vines coil tightly, imitating the curves of joints.</v>
       </c>
-      <c r="T8" s="4" t="str">
+      <c r="T8" s="5" t="str">
         <v>A vivid red adornment—at a distance, it resembles a silk necklace… or dried blood.</v>
       </c>
       <c r="U8" s="3" t="str">
@@ -1584,10 +1594,10 @@
     <row r="15">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
@@ -7970,13 +7980,13 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="13" t="str">
+      <c r="A1" s="10" t="str">
         <v>ItemId</v>
       </c>
-      <c r="B1" s="13" t="str">
+      <c r="B1" s="10" t="str">
         <v>ItemName</v>
       </c>
-      <c r="C1" s="13" t="str">
+      <c r="C1" s="10" t="str">
         <v>Desc</v>
       </c>
       <c r="D1" s="17" t="str">
@@ -7997,13 +8007,13 @@
       <c r="Q1" s="17"/>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="str">
+      <c r="A2" s="10" t="str">
         <v>int</v>
       </c>
-      <c r="B2" s="13" t="str">
+      <c r="B2" s="10" t="str">
         <v>string</v>
       </c>
-      <c r="C2" s="13" t="str">
+      <c r="C2" s="10" t="str">
         <v>string</v>
       </c>
       <c r="D2" s="17" t="str">
@@ -8024,13 +8034,13 @@
       <c r="Q2" s="17"/>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="str">
+      <c r="A3" s="10" t="str">
         <v>Unique ID</v>
       </c>
-      <c r="B3" s="13" t="str">
+      <c r="B3" s="10" t="str">
         <v>Prop Name</v>
       </c>
-      <c r="C3" s="13" t="str">
+      <c r="C3" s="10" t="str">
         <v>Description of the item</v>
       </c>
       <c r="D3" s="17" t="str">
@@ -11909,276 +11919,276 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="str">
+      <c r="A1" s="8" t="str">
         <v>Planet_Id</v>
       </c>
-      <c r="B1" s="9" t="str">
+      <c r="B1" s="8" t="str">
         <v>Planet</v>
       </c>
-      <c r="C1" s="8" t="str">
+      <c r="C1" s="9" t="str">
         <v>Planet_Desc</v>
       </c>
-      <c r="D1" s="8" t="str">
+      <c r="D1" s="9" t="str">
         <v>Planet_need</v>
       </c>
-      <c r="E1" s="8" t="str">
+      <c r="E1" s="9" t="str">
         <v>Planet_icon</v>
       </c>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="7"/>
-      <c r="M1" s="7"/>
-      <c r="N1" s="7"/>
-      <c r="O1" s="7"/>
-      <c r="P1" s="7"/>
-      <c r="Q1" s="7"/>
-      <c r="R1" s="7"/>
-      <c r="S1" s="7"/>
-      <c r="T1" s="7"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="11"/>
+      <c r="K1" s="11"/>
+      <c r="L1" s="11"/>
+      <c r="M1" s="11"/>
+      <c r="N1" s="11"/>
+      <c r="O1" s="11"/>
+      <c r="P1" s="11"/>
+      <c r="Q1" s="11"/>
+      <c r="R1" s="11"/>
+      <c r="S1" s="11"/>
+      <c r="T1" s="11"/>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="str">
+      <c r="A2" s="8" t="str">
         <v>int</v>
       </c>
-      <c r="B2" s="9" t="str">
+      <c r="B2" s="8" t="str">
         <v>string</v>
       </c>
-      <c r="C2" s="8" t="str">
+      <c r="C2" s="9" t="str">
         <v>string</v>
       </c>
-      <c r="D2" s="8" t="str">
+      <c r="D2" s="9" t="str">
         <v>string</v>
       </c>
-      <c r="E2" s="8" t="str">
+      <c r="E2" s="9" t="str">
         <v>string</v>
       </c>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
-      <c r="P2" s="7"/>
-      <c r="Q2" s="7"/>
-      <c r="R2" s="7"/>
-      <c r="S2" s="7"/>
-      <c r="T2" s="7"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="11"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="11"/>
+      <c r="J2" s="11"/>
+      <c r="K2" s="11"/>
+      <c r="L2" s="11"/>
+      <c r="M2" s="11"/>
+      <c r="N2" s="11"/>
+      <c r="O2" s="11"/>
+      <c r="P2" s="11"/>
+      <c r="Q2" s="11"/>
+      <c r="R2" s="11"/>
+      <c r="S2" s="11"/>
+      <c r="T2" s="11"/>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="str">
+      <c r="A3" s="8" t="str">
         <v>唯一id</v>
       </c>
-      <c r="B3" s="9" t="str">
+      <c r="B3" s="8" t="str">
         <v>星球的名字</v>
       </c>
-      <c r="C3" s="8" t="str">
+      <c r="C3" s="9" t="str">
         <v>星球描述文本</v>
       </c>
-      <c r="D3" s="8" t="str">
+      <c r="D3" s="9" t="str">
         <v>星球需求文本</v>
       </c>
-      <c r="E3" s="8" t="str">
+      <c r="E3" s="9" t="str">
         <v>星球icon</v>
       </c>
-      <c r="F3" s="7"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="7"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="7"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="7"/>
-      <c r="M3" s="7"/>
-      <c r="N3" s="7"/>
-      <c r="O3" s="7"/>
-      <c r="P3" s="7"/>
-      <c r="Q3" s="7"/>
-      <c r="R3" s="7"/>
-      <c r="S3" s="7"/>
-      <c r="T3" s="7"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11"/>
+      <c r="J3" s="11"/>
+      <c r="K3" s="11"/>
+      <c r="L3" s="11"/>
+      <c r="M3" s="11"/>
+      <c r="N3" s="11"/>
+      <c r="O3" s="11"/>
+      <c r="P3" s="11"/>
+      <c r="Q3" s="11"/>
+      <c r="R3" s="11"/>
+      <c r="S3" s="11"/>
+      <c r="T3" s="11"/>
     </row>
     <row r="4">
-      <c r="A4" s="4">
+      <c r="A4" s="5">
         <v>1</v>
       </c>
-      <c r="B4" s="4" t="str">
+      <c r="B4" s="5" t="str">
         <v>Budya</v>
       </c>
-      <c r="C4" s="4" t="str">
+      <c r="C4" s="5" t="str">
         <v>An extraterrestrial paradise born from pure, innocent hearts. A world composed of harmless flora and fauna.</v>
       </c>
-      <c r="D4" s="4" t="str">
+      <c r="D4" s="5" t="str">
         <v>Everyone is welcome to join OVO!</v>
       </c>
-      <c r="E4" s="4" t="str">
+      <c r="E4" s="5" t="str">
         <v>Budya_icon</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4">
+      <c r="A5" s="5">
         <v>2</v>
       </c>
-      <c r="B5" s="4" t="str">
+      <c r="B5" s="5" t="str">
         <v>Tonis</v>
       </c>
-      <c r="C5" s="4" t="str">
+      <c r="C5" s="5" t="str">
         <v>Highly commercialized. The designated supplier for the Interstellar Alliance.</v>
       </c>
-      <c r="D5" s="4" t="str">
+      <c r="D5" s="5" t="str">
         <v>Hiring hair stylists. Speak with your hands, come quickly!</v>
       </c>
-      <c r="E5" s="4" t="str">
+      <c r="E5" s="5" t="str">
         <v>Tonis_icon</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4">
+      <c r="A6" s="5">
         <v>3</v>
       </c>
-      <c r="B6" s="4" t="str">
+      <c r="B6" s="5" t="str">
         <v>Shawshank</v>
       </c>
-      <c r="C6" s="4" t="str">
+      <c r="C6" s="5" t="str">
         <v>Over 80% of the planet is ocean. The only landmass hosts the galaxy's most heavily guarded maximum-security prison.</v>
       </c>
-      <c r="D6" s="4" t="str">
+      <c r="D6" s="5" t="str">
         <v>Urgent need for 10 maintenance workers.
 “The highest bounty for an escaped prisoner is 503,333…”</v>
       </c>
-      <c r="E6" s="4" t="str">
+      <c r="E6" s="5" t="str">
         <v>Shawshank_icon</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4">
+      <c r="A7" s="5">
         <v>4</v>
       </c>
-      <c r="B7" s="4" t="str">
+      <c r="B7" s="5" t="str">
         <v>Screw</v>
       </c>
-      <c r="C7" s="4" t="str">
+      <c r="C7" s="5" t="str">
         <v>A collective of intelligent mechanical spirals. The entire planet has been transformed into a massive starship.</v>
       </c>
-      <c r="D7" s="4" t="str">
+      <c r="D7" s="5" t="str">
         <v>Hiring crew members.
 Old exploration-type robots welcome. Only the core needs to be intact.
 The ship has ample space and no wear-and-tear issues.</v>
       </c>
-      <c r="E7" s="4" t="str">
+      <c r="E7" s="5" t="str">
         <v>Screw_icon</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4">
+      <c r="A8" s="5">
         <v>5</v>
       </c>
-      <c r="B8" s="4" t="str">
+      <c r="B8" s="5" t="str">
         <v>Arrakis</v>
       </c>
-      <c r="C8" s="4" t="str">
+      <c r="C8" s="5" t="str">
         <v>Once rich with immense energy sources, now a lawless paradise for outlaws after drying up.</v>
       </c>
-      <c r="D8" s="4" t="str">
+      <c r="D8" s="5" t="str">
         <v>It's a Sicilian message. It means Luca Brasi sleeps withthe fishes.Send it and you take the money.</v>
       </c>
-      <c r="E8" s="4" t="str">
+      <c r="E8" s="5" t="str">
         <v>Arrakis_icon</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4">
+      <c r="A9" s="5">
         <v>6</v>
       </c>
-      <c r="B9" s="4" t="str">
+      <c r="B9" s="5" t="str">
         <v>Lost Eden</v>
       </c>
-      <c r="C9" s="4" t="str">
+      <c r="C9" s="5" t="str">
         <v>A garden of Eden-like bliss. If you can imagine it, you can have endless joy here.</v>
       </c>
-      <c r="D9" s="4" t="str">
+      <c r="D9" s="5" t="str">
         <v>Work? No, come play. Your only responsibility is to make yourself happy — and feel free to tell others how to be even happier.</v>
       </c>
-      <c r="E9" s="4" t="str">
+      <c r="E9" s="5" t="str">
         <v>LostEden_icon</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4">
+      <c r="A10" s="5">
         <v>7</v>
       </c>
-      <c r="B10" s="4" t="str">
+      <c r="B10" s="5" t="str">
         <v>Jelly</v>
       </c>
-      <c r="C10" s="4" t="str">
+      <c r="C10" s="5" t="str">
         <v>The planet's surface is covered in gelatinous material. The favorite amusement park destination for interstellar families with children.</v>
       </c>
-      <c r="D10" s="4" t="str">
+      <c r="D10" s="5" t="str">
         <v>Hiring a Jelly Pit Rescue Assistant. Rescue stuck kids, keep them smiling, stay cheerful. Free park access included.</v>
       </c>
-      <c r="E10" s="4" t="str">
+      <c r="E10" s="5" t="str">
         <v>Jelly_icon</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4">
+      <c r="A11" s="5">
         <v>8</v>
       </c>
-      <c r="B11" s="4" t="str">
+      <c r="B11" s="5" t="str">
         <v>Cinnabar Eye</v>
       </c>
-      <c r="C11" s="4" t="str">
+      <c r="C11" s="5" t="str">
         <v>The atmosphere consists of hydrogen and helium. The largest gas giant in the Kartos Star System.</v>
       </c>
-      <c r="D11" s="4" t="str">
+      <c r="D11" s="5" t="str">
         <v>Position: Lead Scout
 Duties: Explore uncharted areas and collect resource and risk data.
 Compensation: Paid per validated report. Reports are archived only; retrieval of personnel is not guaranteed.</v>
       </c>
-      <c r="E11" s="4" t="str">
+      <c r="E11" s="5" t="str">
         <v>CinnabarEye_icon</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4">
+      <c r="A12" s="5">
         <v>9</v>
       </c>
-      <c r="B12" s="4" t="str">
+      <c r="B12" s="5" t="str">
         <v>Surukan</v>
       </c>
-      <c r="C12" s="4" t="str">
+      <c r="C12" s="5" t="str">
         <v>A realm of serene silence. Every citizen focuses solely on themselves.</v>
       </c>
-      <c r="D12" s="4" t="str">
+      <c r="D12" s="5" t="str">
         <v>Position: Boundary Keeper
 Duties: Protect personal boundaries
 Requirements: Fair
 </v>
       </c>
-      <c r="E12" s="4" t="str">
+      <c r="E12" s="5" t="str">
         <v>Surukan_icon</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4">
+      <c r="A13" s="5">
         <v>10</v>
       </c>
-      <c r="B13" s="4" t="str">
+      <c r="B13" s="5" t="str">
         <v>Tarasus</v>
       </c>
-      <c r="C13" s="4" t="str">
+      <c r="C13" s="5" t="str">
         <v>An ocean of trees. Countless roots intertwine and fuse together, united as one.</v>
       </c>
-      <c r="D13" s="4" t="str">
+      <c r="D13" s="5" t="str">
         <v>Roots entwined with roots — though they occasionally tangle and twist. The old village chief has stiff legs and speaks slowly. We're short a translator who can listen to both sides of the tree-root conversations.</v>
       </c>
-      <c r="E13" s="4" t="str">
+      <c r="E13" s="5" t="str">
         <v>Tarasus_icon</v>
       </c>
     </row>
@@ -12763,65 +12773,65 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="13" t="str">
+      <c r="A1" s="10" t="str">
         <v>Remarks</v>
       </c>
-      <c r="B1" s="13" t="str">
+      <c r="B1" s="10" t="str">
         <v>DialogueId</v>
       </c>
-      <c r="C1" s="13" t="str">
+      <c r="C1" s="10" t="str">
         <v>Text</v>
       </c>
-      <c r="D1" s="13" t="str">
+      <c r="D1" s="10" t="str">
         <v>next</v>
       </c>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="7"/>
-      <c r="M1" s="7"/>
-      <c r="N1" s="7"/>
-      <c r="O1" s="7"/>
-      <c r="P1" s="7"/>
-      <c r="Q1" s="7"/>
-      <c r="R1" s="7"/>
-      <c r="S1" s="7"/>
-      <c r="T1" s="7"/>
-      <c r="U1" s="7"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="11"/>
+      <c r="K1" s="11"/>
+      <c r="L1" s="11"/>
+      <c r="M1" s="11"/>
+      <c r="N1" s="11"/>
+      <c r="O1" s="11"/>
+      <c r="P1" s="11"/>
+      <c r="Q1" s="11"/>
+      <c r="R1" s="11"/>
+      <c r="S1" s="11"/>
+      <c r="T1" s="11"/>
+      <c r="U1" s="11"/>
     </row>
     <row r="2">
-      <c r="A2" s="13"/>
-      <c r="B2" s="13" t="str">
+      <c r="A2" s="10"/>
+      <c r="B2" s="10" t="str">
         <v>int</v>
       </c>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
-      <c r="P2" s="7"/>
-      <c r="Q2" s="7"/>
-      <c r="R2" s="7"/>
-      <c r="S2" s="7"/>
-      <c r="T2" s="7"/>
-      <c r="U2" s="7"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="11"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="11"/>
+      <c r="J2" s="11"/>
+      <c r="K2" s="11"/>
+      <c r="L2" s="11"/>
+      <c r="M2" s="11"/>
+      <c r="N2" s="11"/>
+      <c r="O2" s="11"/>
+      <c r="P2" s="11"/>
+      <c r="Q2" s="11"/>
+      <c r="R2" s="11"/>
+      <c r="S2" s="11"/>
+      <c r="T2" s="11"/>
+      <c r="U2" s="11"/>
     </row>
     <row r="3">
-      <c r="A3" s="13"/>
-      <c r="B3" s="13"/>
-      <c r="C3" s="13" t="str">
+      <c r="A3" s="10"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="10" t="str">
         <v>Name: Speaker Content
 Special Speaker Chice
 “Choice
@@ -12829,51 +12839,51 @@
 Option 2 text content | 0
 Text content of Option 3 | 0 represents end</v>
       </c>
-      <c r="D3" s="13"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="7"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="7"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="7"/>
-      <c r="M3" s="7"/>
-      <c r="N3" s="7"/>
-      <c r="O3" s="7"/>
-      <c r="P3" s="7">
+      <c r="D3" s="10"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11"/>
+      <c r="J3" s="11"/>
+      <c r="K3" s="11"/>
+      <c r="L3" s="11"/>
+      <c r="M3" s="11"/>
+      <c r="N3" s="11"/>
+      <c r="O3" s="11"/>
+      <c r="P3" s="11">
         <v>5</v>
       </c>
-      <c r="Q3" s="7"/>
-      <c r="R3" s="7"/>
-      <c r="S3" s="7"/>
-      <c r="T3" s="7"/>
-      <c r="U3" s="7"/>
+      <c r="Q3" s="11"/>
+      <c r="R3" s="11"/>
+      <c r="S3" s="11"/>
+      <c r="T3" s="11"/>
+      <c r="U3" s="11"/>
     </row>
     <row customHeight="true" ht="28" r="4">
-      <c r="A4" s="20" t="str">
+      <c r="A4" s="23" t="str">
         <v>Performance 1 Opening</v>
       </c>
-      <c r="B4" s="20"/>
-      <c r="C4" s="20"/>
-      <c r="D4" s="20"/>
-      <c r="E4" s="21"/>
-      <c r="F4" s="21"/>
-      <c r="G4" s="21"/>
-      <c r="H4" s="21"/>
-      <c r="I4" s="21"/>
-      <c r="J4" s="21"/>
-      <c r="K4" s="21"/>
-      <c r="L4" s="21"/>
-      <c r="M4" s="21"/>
-      <c r="N4" s="21"/>
-      <c r="O4" s="21"/>
-      <c r="P4" s="21"/>
-      <c r="Q4" s="21"/>
-      <c r="R4" s="21"/>
-      <c r="S4" s="21"/>
-      <c r="T4" s="21"/>
-      <c r="U4" s="21"/>
+      <c r="B4" s="23"/>
+      <c r="C4" s="23"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
+      <c r="G4" s="18"/>
+      <c r="H4" s="18"/>
+      <c r="I4" s="18"/>
+      <c r="J4" s="18"/>
+      <c r="K4" s="18"/>
+      <c r="L4" s="18"/>
+      <c r="M4" s="18"/>
+      <c r="N4" s="18"/>
+      <c r="O4" s="18"/>
+      <c r="P4" s="18"/>
+      <c r="Q4" s="18"/>
+      <c r="R4" s="18"/>
+      <c r="S4" s="18"/>
+      <c r="T4" s="18"/>
+      <c r="U4" s="18"/>
     </row>
     <row customHeight="true" ht="86" r="5">
       <c r="A5" s="6"/>
@@ -12888,23 +12898,23 @@
 No|3</v>
       </c>
       <c r="D5" s="6"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2"/>
-      <c r="M5" s="2"/>
-      <c r="N5" s="2"/>
-      <c r="O5" s="2"/>
-      <c r="P5" s="2"/>
-      <c r="Q5" s="2"/>
-      <c r="R5" s="2"/>
-      <c r="S5" s="2"/>
-      <c r="T5" s="2"/>
-      <c r="U5" s="2"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="14"/>
+      <c r="H5" s="14"/>
+      <c r="I5" s="14"/>
+      <c r="J5" s="14"/>
+      <c r="K5" s="14"/>
+      <c r="L5" s="14"/>
+      <c r="M5" s="14"/>
+      <c r="N5" s="14"/>
+      <c r="O5" s="14"/>
+      <c r="P5" s="14"/>
+      <c r="Q5" s="14"/>
+      <c r="R5" s="14"/>
+      <c r="S5" s="14"/>
+      <c r="T5" s="14"/>
+      <c r="U5" s="14"/>
     </row>
     <row r="6">
       <c r="A6" s="6"/>
@@ -12918,23 +12928,23 @@
       <c r="D6" s="6">
         <v>4</v>
       </c>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2"/>
-      <c r="M6" s="2"/>
-      <c r="N6" s="2"/>
-      <c r="O6" s="2"/>
-      <c r="P6" s="2"/>
-      <c r="Q6" s="2"/>
-      <c r="R6" s="2"/>
-      <c r="S6" s="2"/>
-      <c r="T6" s="2"/>
-      <c r="U6" s="2"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="14"/>
+      <c r="H6" s="14"/>
+      <c r="I6" s="14"/>
+      <c r="J6" s="14"/>
+      <c r="K6" s="14"/>
+      <c r="L6" s="14"/>
+      <c r="M6" s="14"/>
+      <c r="N6" s="14"/>
+      <c r="O6" s="14"/>
+      <c r="P6" s="14"/>
+      <c r="Q6" s="14"/>
+      <c r="R6" s="14"/>
+      <c r="S6" s="14"/>
+      <c r="T6" s="14"/>
+      <c r="U6" s="14"/>
     </row>
     <row r="7">
       <c r="A7" s="6"/>
@@ -12949,23 +12959,23 @@
       <c r="D7" s="6">
         <v>4</v>
       </c>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
-      <c r="N7" s="2"/>
-      <c r="O7" s="2"/>
-      <c r="P7" s="2"/>
-      <c r="Q7" s="2"/>
-      <c r="R7" s="2"/>
-      <c r="S7" s="2"/>
-      <c r="T7" s="2"/>
-      <c r="U7" s="2"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="14"/>
+      <c r="H7" s="14"/>
+      <c r="I7" s="14"/>
+      <c r="J7" s="14"/>
+      <c r="K7" s="14"/>
+      <c r="L7" s="14"/>
+      <c r="M7" s="14"/>
+      <c r="N7" s="14"/>
+      <c r="O7" s="14"/>
+      <c r="P7" s="14"/>
+      <c r="Q7" s="14"/>
+      <c r="R7" s="14"/>
+      <c r="S7" s="14"/>
+      <c r="T7" s="14"/>
+      <c r="U7" s="14"/>
     </row>
     <row r="8">
       <c r="A8" s="6"/>
@@ -12984,51 +12994,51 @@
 Manager: Try not to get eaten.Ciao~</v>
       </c>
       <c r="D8" s="6"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
-      <c r="M8" s="2"/>
-      <c r="N8" s="2"/>
-      <c r="O8" s="2"/>
-      <c r="P8" s="2"/>
-      <c r="Q8" s="2"/>
-      <c r="R8" s="2"/>
-      <c r="S8" s="2"/>
-      <c r="T8" s="2"/>
-      <c r="U8" s="2"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="14"/>
+      <c r="H8" s="14"/>
+      <c r="I8" s="14"/>
+      <c r="J8" s="14"/>
+      <c r="K8" s="14"/>
+      <c r="L8" s="14"/>
+      <c r="M8" s="14"/>
+      <c r="N8" s="14"/>
+      <c r="O8" s="14"/>
+      <c r="P8" s="14"/>
+      <c r="Q8" s="14"/>
+      <c r="R8" s="14"/>
+      <c r="S8" s="14"/>
+      <c r="T8" s="14"/>
+      <c r="U8" s="14"/>
     </row>
     <row r="9">
-      <c r="A9" s="20" t="str">
+      <c r="A9" s="23" t="str">
         <v>Performance 2 Beginner's Guide</v>
       </c>
-      <c r="B9" s="20"/>
-      <c r="C9" s="20"/>
-      <c r="D9" s="20"/>
-      <c r="E9" s="21"/>
-      <c r="F9" s="21"/>
-      <c r="G9" s="21"/>
-      <c r="H9" s="21"/>
-      <c r="I9" s="21"/>
-      <c r="J9" s="21"/>
-      <c r="K9" s="21"/>
-      <c r="L9" s="21"/>
-      <c r="M9" s="21"/>
-      <c r="N9" s="21"/>
-      <c r="O9" s="21"/>
-      <c r="P9" s="21"/>
-      <c r="Q9" s="21"/>
-      <c r="R9" s="21"/>
-      <c r="S9" s="21"/>
-      <c r="T9" s="21"/>
-      <c r="U9" s="21"/>
+      <c r="B9" s="23"/>
+      <c r="C9" s="23"/>
+      <c r="D9" s="23"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="18"/>
+      <c r="G9" s="18"/>
+      <c r="H9" s="18"/>
+      <c r="I9" s="18"/>
+      <c r="J9" s="18"/>
+      <c r="K9" s="18"/>
+      <c r="L9" s="18"/>
+      <c r="M9" s="18"/>
+      <c r="N9" s="18"/>
+      <c r="O9" s="18"/>
+      <c r="P9" s="18"/>
+      <c r="Q9" s="18"/>
+      <c r="R9" s="18"/>
+      <c r="S9" s="18"/>
+      <c r="T9" s="18"/>
+      <c r="U9" s="18"/>
     </row>
     <row r="10">
-      <c r="A10" s="18"/>
+      <c r="A10" s="22"/>
       <c r="B10" s="6">
         <v>16</v>
       </c>
@@ -13044,7 +13054,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="18"/>
+      <c r="A11" s="22"/>
       <c r="B11" s="6">
         <v>17</v>
       </c>
@@ -13057,7 +13067,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="18"/>
+      <c r="A12" s="22"/>
       <c r="B12" s="6">
         <v>18</v>
       </c>
@@ -13072,7 +13082,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="18"/>
+      <c r="A13" s="22"/>
       <c r="B13" s="6">
         <v>19</v>
       </c>
@@ -13084,178 +13094,178 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="18"/>
+      <c r="A14" s="22"/>
       <c r="B14" s="6">
         <v>20</v>
       </c>
-      <c r="C14" s="5" t="str">
+      <c r="C14" s="2" t="str">
         <v>Woofie: I believe in you, rookie! Woof!</v>
       </c>
-      <c r="D14" s="5"/>
+      <c r="D14" s="2"/>
     </row>
     <row r="15">
-      <c r="A15" s="22" t="str">
+      <c r="A15" s="20" t="str">
         <v>Performance 3 ending</v>
       </c>
-      <c r="B15" s="23"/>
-      <c r="C15" s="23"/>
-      <c r="D15" s="23"/>
-      <c r="E15" s="21"/>
-      <c r="F15" s="21"/>
-      <c r="G15" s="21"/>
-      <c r="H15" s="21"/>
-      <c r="I15" s="21"/>
-      <c r="J15" s="21"/>
-      <c r="K15" s="21"/>
-      <c r="L15" s="21"/>
-      <c r="M15" s="21"/>
-      <c r="N15" s="21"/>
-      <c r="O15" s="21"/>
-      <c r="P15" s="21"/>
-      <c r="Q15" s="21"/>
-      <c r="R15" s="21"/>
-      <c r="S15" s="21"/>
-      <c r="T15" s="21"/>
-      <c r="U15" s="21"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="18"/>
+      <c r="H15" s="18"/>
+      <c r="I15" s="18"/>
+      <c r="J15" s="18"/>
+      <c r="K15" s="18"/>
+      <c r="L15" s="18"/>
+      <c r="M15" s="18"/>
+      <c r="N15" s="18"/>
+      <c r="O15" s="18"/>
+      <c r="P15" s="18"/>
+      <c r="Q15" s="18"/>
+      <c r="R15" s="18"/>
+      <c r="S15" s="18"/>
+      <c r="T15" s="18"/>
+      <c r="U15" s="18"/>
     </row>
     <row r="16">
-      <c r="A16" s="18"/>
-      <c r="B16" s="19">
+      <c r="A16" s="22"/>
+      <c r="B16" s="21">
         <v>5</v>
       </c>
-      <c r="C16" s="18" t="str">
+      <c r="C16" s="22" t="str">
         <v>Manager: Oh! Looks like you survived your first day on the job.
 Manager: Let me see that performance report...
 Manager: [n] satisfied, [n] average, [n] complaints.</v>
       </c>
-      <c r="D16" s="18"/>
+      <c r="D16" s="22"/>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="str">
+      <c r="A17" s="22" t="str">
         <v>(When 0 mistakes)</v>
       </c>
-      <c r="B17" s="19">
+      <c r="B17" s="21">
         <v>6</v>
       </c>
-      <c r="C17" s="19" t="str">
+      <c r="C17" s="21" t="str">
         <v>Manager: Well, well. You're sharper than you look.
 Choice
 Heh~|11
 Not bad, right?|11</v>
       </c>
-      <c r="D17" s="19"/>
+      <c r="D17" s="21"/>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="str">
+      <c r="A18" s="22" t="str">
         <v>(When 1 or 2 mistakes)</v>
       </c>
-      <c r="B18" s="19">
+      <c r="B18" s="21">
         <v>7</v>
       </c>
-      <c r="C18" s="19" t="str">
+      <c r="C18" s="21" t="str">
         <v>Manager: Hm. You're taking this seriously. I like that.
 Choice
 Heh~|12
 Not bad, right?|12</v>
       </c>
-      <c r="D18" s="19"/>
+      <c r="D18" s="21"/>
     </row>
     <row r="19">
-      <c r="A19" s="18" t="str">
+      <c r="A19" s="22" t="str">
         <v>(When 3 or 4 mistakes)</v>
       </c>
-      <c r="B19" s="19">
+      <c r="B19" s="21">
         <v>8</v>
       </c>
-      <c r="C19" s="19" t="str">
+      <c r="C19" s="21" t="str">
         <v>Manager: Looks like you've still got a lot to learn.
 Choice
 Heh~|13
 Not bad, right?|13</v>
       </c>
-      <c r="D19" s="19"/>
+      <c r="D19" s="21"/>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="str">
+      <c r="A20" s="22" t="str">
         <v>(When 5 mistakes)</v>
       </c>
-      <c r="B20" s="19">
+      <c r="B20" s="21">
         <v>9</v>
       </c>
-      <c r="C20" s="19" t="str">
+      <c r="C20" s="21" t="str">
         <v>Manager: Good grief. Were you making decisions with your elbows?
 Choice
 Heh~|14
 Not bad, right?|14</v>
       </c>
-      <c r="D20" s="19"/>
+      <c r="D20" s="21"/>
     </row>
     <row r="21">
-      <c r="A21" s="18"/>
-      <c r="B21" s="19">
+      <c r="A21" s="22"/>
+      <c r="B21" s="21">
         <v>11</v>
       </c>
-      <c r="C21" s="19" t="str">
+      <c r="C21" s="21" t="str">
         <v>Manager: I knew I wasn't wrong about you.
 Manager: Talented inspectors are getting harder to find these days.
 Manager: Keep this up, and you might even earn yourself a promotion to headquarters before long.</v>
       </c>
-      <c r="D21" s="19">
+      <c r="D21" s="21">
         <v>15</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="18"/>
-      <c r="B22" s="19">
+      <c r="A22" s="22"/>
+      <c r="B22" s="21">
         <v>12</v>
       </c>
-      <c r="C22" s="19" t="str">
+      <c r="C22" s="21" t="str">
         <v>Manager: Confidence is good. Keep that fire in you.
 Manager: Just don't slack off on your training.
 Manager: And ask your senior, Woofie, plenty of questions while you can.</v>
       </c>
-      <c r="D22" s="19">
+      <c r="D22" s="21">
         <v>15</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="18"/>
-      <c r="B23" s="19">
+      <c r="A23" s="22"/>
+      <c r="B23" s="21">
         <v>13</v>
       </c>
-      <c r="C23" s="19" t="str">
+      <c r="C23" s="21" t="str">
         <v>Manager: Hah. Got jokes, huh?
 Manager: Still, for a rookie to make it this far already... not bad at all.</v>
       </c>
-      <c r="D23" s="19">
+      <c r="D23" s="21">
         <v>15</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="18"/>
-      <c r="B24" s="19">
+      <c r="A24" s="22"/>
+      <c r="B24" s="21">
         <v>14</v>
       </c>
-      <c r="C24" s="19" t="str">
+      <c r="C24" s="21" t="str">
         <v>Manager: Oh please, don't try that cute routine on me.
 Manager: I've seen every trick in the book.
 Manager: Hit the books tonight, or next time I'm shipping you off to Planet Dummy.</v>
       </c>
-      <c r="D24" s="19">
+      <c r="D24" s="21">
         <v>15</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="18"/>
-      <c r="B25" s="19">
+      <c r="A25" s="22"/>
+      <c r="B25" s="21">
         <v>15</v>
       </c>
-      <c r="C25" s="18" t="str">
+      <c r="C25" s="22" t="str">
         <v>Manager: Alright, that's enough for today.
 Manager: No matter what kind of work you do, remember to eat well, stay hydrated, and leave work on time.
 Managerz：See you tomorrow！ Ciao~</v>
       </c>
-      <c r="D25" s="18"/>
+      <c r="D25" s="22"/>
     </row>
   </sheetData>
 </worksheet>

--- a/Assets/GameData/database.xlsx
+++ b/Assets/GameData/database.xlsx
@@ -104,30 +104,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF258"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF258"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF258"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF258"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFD5F6F2"/>
         <bgColor/>
       </patternFill>
@@ -170,6 +146,30 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFF258"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF258"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF258"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF258"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFD5F6F2"/>
         <bgColor/>
       </patternFill>
@@ -183,18 +183,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF258"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8F959E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8F959E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -224,7 +212,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF8F959E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFD5F6F2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8F959E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -416,47 +416,47 @@
     <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0">
       <alignment vertical="center" wrapText="true"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="2" fillId="2" fontId="1" numFmtId="0" xfId="0">
+    <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="3" fillId="2" fontId="2" numFmtId="0" xfId="0">
       <alignment vertical="center" wrapText="true"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="3" fillId="3" fontId="2" numFmtId="0" xfId="0">
+    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="4" fillId="3" fontId="1" numFmtId="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="true"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="4" fillId="4" fontId="1" numFmtId="0" xfId="0">
+    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="5" fillId="4" fontId="2" numFmtId="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="true"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="5" fillId="5" fontId="2" numFmtId="0" xfId="0">
+    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="6" fillId="5" fontId="2" numFmtId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="6" fillId="6" fontId="1" numFmtId="0" xfId="0">
+    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="7" fillId="6" fontId="2" numFmtId="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="8" fillId="7" fontId="1" numFmtId="0" xfId="0">
+      <alignment vertical="center" wrapText="true"/>
+    </xf>
+    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="9" fillId="8" fontId="1" numFmtId="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="10" fillId="9" fontId="1" numFmtId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="11" fillId="10" fontId="1" numFmtId="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="true"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="7" fillId="7" fontId="2" numFmtId="0" xfId="0">
-      <alignment vertical="center" wrapText="true"/>
+    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="12" fillId="11" fontId="2" numFmtId="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="8" fillId="8" fontId="2" numFmtId="0" xfId="0">
+    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="13" fillId="12" fontId="2" numFmtId="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="true"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="9" fillId="9" fontId="2" numFmtId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="10" fillId="10" fontId="2" numFmtId="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="11" fillId="11" fontId="1" numFmtId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="12" fillId="12" fontId="1" numFmtId="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="13" fillId="13" fontId="3" numFmtId="0" xfId="0">
+    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="14" fillId="13" fontId="3" numFmtId="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="true"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="14" fillId="14" fontId="1" numFmtId="0" xfId="0">
+    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="15" fillId="14" fontId="1" numFmtId="0" xfId="0">
       <alignment vertical="center" wrapText="true"/>
-    </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="15" fillId="0" fontId="1" numFmtId="0" xfId="0">
-      <alignment vertical="center"/>
     </xf>
     <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="16" fillId="0" fontId="2" numFmtId="0" xfId="0">
       <alignment vertical="center"/>
@@ -465,25 +465,25 @@
       <alignment vertical="center" wrapText="true"/>
     </xf>
     <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="18" fillId="16" fontId="1" numFmtId="0" xfId="0">
-      <alignment vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="19" fillId="17" fontId="2" numFmtId="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="true"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="20" fillId="18" fontId="1" numFmtId="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment vertical="center"/>
     </xf>
     <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="21" fillId="19" fontId="2" numFmtId="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="22" fillId="20" fontId="2" numFmtId="0" xfId="0">
+    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="22" fillId="20" fontId="1" numFmtId="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="23" fillId="21" fontId="1" numFmtId="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment vertical="center"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="24" fillId="22" fontId="1" numFmtId="0" xfId="0">
-      <alignment vertical="center"/>
+    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="24" fillId="22" fontId="2" numFmtId="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="true"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -828,289 +828,289 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="str">
+      <c r="A1" s="11" t="str">
         <v>CharacterId</v>
       </c>
-      <c r="B1" s="4" t="str">
+      <c r="B1" s="11" t="str">
         <v>Name</v>
       </c>
-      <c r="C1" s="4" t="str">
+      <c r="C1" s="11" t="str">
         <v>race</v>
       </c>
-      <c r="D1" s="4" t="str">
+      <c r="D1" s="11" t="str">
         <v>Desc</v>
       </c>
-      <c r="E1" s="4" t="str">
+      <c r="E1" s="11" t="str">
         <v>Planet</v>
       </c>
-      <c r="F1" s="4" t="str">
+      <c r="F1" s="11" t="str">
         <v>PlanetOption</v>
       </c>
-      <c r="G1" s="4" t="str">
+      <c r="G1" s="11" t="str">
         <v>Items</v>
       </c>
-      <c r="H1" s="2" t="str">
+      <c r="H1" s="8" t="str">
         <v>Question1</v>
       </c>
-      <c r="I1" s="2" t="str">
+      <c r="I1" s="8" t="str">
         <v>keyword1</v>
       </c>
-      <c r="J1" s="2" t="str">
+      <c r="J1" s="8" t="str">
         <v>Answer1</v>
       </c>
-      <c r="K1" s="2" t="str">
+      <c r="K1" s="8" t="str">
         <v>Question2</v>
       </c>
-      <c r="L1" s="2" t="str">
+      <c r="L1" s="8" t="str">
         <v>keyword1</v>
       </c>
-      <c r="M1" s="2" t="str">
+      <c r="M1" s="8" t="str">
         <v>Answer2</v>
       </c>
-      <c r="N1" s="2" t="str">
+      <c r="N1" s="8" t="str">
         <v>Question3</v>
       </c>
-      <c r="O1" s="2" t="str">
+      <c r="O1" s="8" t="str">
         <v>keyword1</v>
       </c>
-      <c r="P1" s="2" t="str">
+      <c r="P1" s="8" t="str">
         <v>Answer3</v>
       </c>
-      <c r="Q1" s="5" t="str">
+      <c r="Q1" s="12" t="str">
         <v>glitter</v>
       </c>
-      <c r="R1" s="3" t="str">
+      <c r="R1" s="13" t="str">
         <v>Profile_picture</v>
       </c>
-      <c r="S1" s="3" t="str">
+      <c r="S1" s="13" t="str">
         <v>Full_appearance</v>
       </c>
-      <c r="T1" s="3" t="str">
+      <c r="T1" s="13" t="str">
         <v>Full_S</v>
       </c>
-      <c r="U1" s="3" t="str">
+      <c r="U1" s="13" t="str">
         <v>Full_X</v>
       </c>
-      <c r="V1" s="2"/>
-      <c r="W1" s="2"/>
-      <c r="X1" s="2"/>
-      <c r="Y1" s="2"/>
-      <c r="Z1" s="2"/>
-      <c r="AA1" s="2"/>
-      <c r="AB1" s="2"/>
-      <c r="AC1" s="2"/>
-      <c r="AD1" s="2"/>
+      <c r="V1" s="8"/>
+      <c r="W1" s="8"/>
+      <c r="X1" s="8"/>
+      <c r="Y1" s="8"/>
+      <c r="Z1" s="8"/>
+      <c r="AA1" s="8"/>
+      <c r="AB1" s="8"/>
+      <c r="AC1" s="8"/>
+      <c r="AD1" s="8"/>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="str">
+      <c r="A2" s="11" t="str">
         <v>int</v>
       </c>
-      <c r="B2" s="4" t="str">
+      <c r="B2" s="11" t="str">
         <v>string</v>
       </c>
-      <c r="C2" s="4" t="str">
+      <c r="C2" s="11" t="str">
         <v>string</v>
       </c>
-      <c r="D2" s="4" t="str">
+      <c r="D2" s="11" t="str">
         <v>string</v>
       </c>
-      <c r="E2" s="4" t="str">
+      <c r="E2" s="11" t="str">
         <v>string</v>
       </c>
-      <c r="F2" s="4" t="str">
+      <c r="F2" s="11" t="str">
         <v>string</v>
       </c>
-      <c r="G2" s="4" t="str">
+      <c r="G2" s="11" t="str">
         <v>string</v>
       </c>
-      <c r="H2" s="2" t="str">
+      <c r="H2" s="8" t="str">
         <v>string</v>
       </c>
-      <c r="I2" s="2" t="str">
+      <c r="I2" s="8" t="str">
         <v>string</v>
       </c>
-      <c r="J2" s="2" t="str">
+      <c r="J2" s="8" t="str">
         <v>string</v>
       </c>
-      <c r="K2" s="2" t="str">
+      <c r="K2" s="8" t="str">
         <v>string</v>
       </c>
-      <c r="L2" s="2" t="str">
+      <c r="L2" s="8" t="str">
         <v>string</v>
       </c>
-      <c r="M2" s="2" t="str">
+      <c r="M2" s="8" t="str">
         <v>string</v>
       </c>
-      <c r="N2" s="2" t="str">
+      <c r="N2" s="8" t="str">
         <v>string</v>
       </c>
-      <c r="O2" s="2" t="str">
+      <c r="O2" s="8" t="str">
         <v>string</v>
       </c>
-      <c r="P2" s="2" t="str">
+      <c r="P2" s="8" t="str">
         <v>string</v>
       </c>
-      <c r="Q2" s="2" t="str">
+      <c r="Q2" s="8" t="str">
         <v>string</v>
       </c>
-      <c r="R2" s="3" t="str">
+      <c r="R2" s="13" t="str">
         <v>string</v>
       </c>
-      <c r="S2" s="3" t="str">
+      <c r="S2" s="13" t="str">
         <v>string</v>
       </c>
-      <c r="T2" s="3" t="str">
+      <c r="T2" s="13" t="str">
         <v>string</v>
       </c>
-      <c r="U2" s="3" t="str">
+      <c r="U2" s="13" t="str">
         <v>string</v>
       </c>
-      <c r="V2" s="2"/>
-      <c r="W2" s="2"/>
-      <c r="X2" s="2"/>
-      <c r="Y2" s="2"/>
-      <c r="Z2" s="2"/>
-      <c r="AA2" s="2"/>
-      <c r="AB2" s="2"/>
-      <c r="AC2" s="2"/>
-      <c r="AD2" s="2"/>
+      <c r="V2" s="8"/>
+      <c r="W2" s="8"/>
+      <c r="X2" s="8"/>
+      <c r="Y2" s="8"/>
+      <c r="Z2" s="8"/>
+      <c r="AA2" s="8"/>
+      <c r="AB2" s="8"/>
+      <c r="AC2" s="8"/>
+      <c r="AD2" s="8"/>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="str">
+      <c r="A3" s="11" t="str">
         <v>唯一id</v>
       </c>
-      <c r="B3" s="12" t="str" xml:space="preserve">
+      <c r="B3" s="9" t="str" xml:space="preserve">
         <v> 角色的姓名</v>
       </c>
-      <c r="C3" s="4" t="str">
+      <c r="C3" s="11" t="str">
         <v>种族</v>
       </c>
-      <c r="D3" s="4" t="str">
+      <c r="D3" s="11" t="str">
         <v>描述</v>
       </c>
-      <c r="E3" s="4" t="str">
+      <c r="E3" s="11" t="str">
         <v>星球</v>
       </c>
-      <c r="F3" s="4" t="str">
+      <c r="F3" s="11" t="str">
         <v>备选星球</v>
       </c>
-      <c r="G3" s="4" t="str">
+      <c r="G3" s="11" t="str">
         <v>小动物携带的道具ID用"|"分割</v>
       </c>
-      <c r="H3" s="11" t="str">
+      <c r="H3" s="10" t="str">
         <v>第一个问题</v>
       </c>
-      <c r="I3" s="11" t="str">
+      <c r="I3" s="10" t="str">
         <v>关键字1</v>
       </c>
-      <c r="J3" s="11" t="str">
+      <c r="J3" s="10" t="str">
         <v>回答一对应的prefab资源的名字</v>
       </c>
-      <c r="K3" s="11" t="str">
+      <c r="K3" s="10" t="str">
         <v>第二个问题</v>
       </c>
-      <c r="L3" s="11" t="str">
+      <c r="L3" s="10" t="str">
         <v>关键字2</v>
       </c>
-      <c r="M3" s="11" t="str">
+      <c r="M3" s="10" t="str">
         <v>回答二对应的prefab资源的名字</v>
       </c>
-      <c r="N3" s="11" t="str">
+      <c r="N3" s="10" t="str">
         <v>第三个问题</v>
       </c>
-      <c r="O3" s="11" t="str">
+      <c r="O3" s="10" t="str">
         <v>关键字3</v>
       </c>
-      <c r="P3" s="11" t="str">
+      <c r="P3" s="10" t="str">
         <v>回答三对应的prefab资源的名字</v>
       </c>
-      <c r="Q3" s="5" t="str">
+      <c r="Q3" s="12" t="str">
         <v>闪光点Prefab</v>
       </c>
-      <c r="R3" s="10" t="str">
+      <c r="R3" s="7" t="str">
         <v>profile头像</v>
       </c>
-      <c r="S3" s="10" t="str">
+      <c r="S3" s="7" t="str">
         <v>窗口大图1920*1080</v>
       </c>
-      <c r="T3" s="10" t="str">
+      <c r="T3" s="7" t="str">
         <v>滤波器全身Scan</v>
       </c>
-      <c r="U3" s="10" t="str">
+      <c r="U3" s="7" t="str">
         <v>全身x光滤波器</v>
       </c>
-      <c r="V3" s="2"/>
-      <c r="W3" s="2"/>
-      <c r="X3" s="2"/>
-      <c r="Y3" s="2"/>
-      <c r="Z3" s="2"/>
-      <c r="AA3" s="2"/>
-      <c r="AB3" s="2"/>
-      <c r="AC3" s="2"/>
-      <c r="AD3" s="2"/>
+      <c r="V3" s="8"/>
+      <c r="W3" s="8"/>
+      <c r="X3" s="8"/>
+      <c r="Y3" s="8"/>
+      <c r="Z3" s="8"/>
+      <c r="AA3" s="8"/>
+      <c r="AB3" s="8"/>
+      <c r="AC3" s="8"/>
+      <c r="AD3" s="8"/>
     </row>
     <row customHeight="true" ht="60" r="4">
-      <c r="A4" s="6">
+      <c r="A4" s="4">
         <v>1</v>
       </c>
-      <c r="B4" s="7" t="str">
+      <c r="B4" s="3" t="str">
         <v>Groot</v>
       </c>
-      <c r="C4" s="6" t="str">
+      <c r="C4" s="4" t="str">
         <v>Sprout</v>
       </c>
-      <c r="D4" s="6" t="str">
+      <c r="D4" s="4" t="str">
         <v>Plant-like sprouts grow on its antennae. Its jagged, tooth-like body serves as perfect camouflage to evade natural enemies.</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="4">
         <v>1</v>
       </c>
-      <c r="F4" s="8" t="str">
+      <c r="F4" s="5" t="str">
         <v>7|8|1</v>
       </c>
-      <c r="G4" s="8" t="str">
+      <c r="G4" s="5" t="str">
         <v>1|2</v>
       </c>
-      <c r="H4" s="7" t="str">
+      <c r="H4" s="3" t="str">
         <v>Are those black dots on your body your eyes?</v>
       </c>
-      <c r="I4" s="7" t="str">
+      <c r="I4" s="3" t="str">
         <v>Eyes</v>
       </c>
-      <c r="J4" s="7" t="str">
+      <c r="J4" s="3" t="str">
         <v>Groot_prefab_1</v>
       </c>
-      <c r="K4" s="7" t="str">
+      <c r="K4" s="3" t="str">
         <v>What is the purpose of the small bud on the head?</v>
       </c>
-      <c r="L4" s="7" t="str">
+      <c r="L4" s="3" t="str">
         <v>Sprout</v>
       </c>
-      <c r="M4" s="7" t="str">
+      <c r="M4" s="3" t="str">
         <v>Groot_prefab_2</v>
       </c>
-      <c r="N4" s="7" t="str">
+      <c r="N4" s="3" t="str">
         <v>What are the kettle and the soil for?</v>
       </c>
-      <c r="O4" s="7" t="str">
-        <v>Water bottle and soil</v>
-      </c>
-      <c r="P4" s="7" t="str">
+      <c r="O4" s="3" t="str">
+        <v>Kettle and soil</v>
+      </c>
+      <c r="P4" s="3" t="str">
         <v>Groot_prefab_3</v>
       </c>
-      <c r="Q4" s="9" t="str">
+      <c r="Q4" s="6" t="str">
         <v>Groot_glitter</v>
       </c>
-      <c r="R4" s="7" t="str">
+      <c r="R4" s="3" t="str">
         <v>Groot_Profile</v>
       </c>
-      <c r="S4" s="7" t="str">
+      <c r="S4" s="3" t="str">
         <v>Groot_appearance</v>
       </c>
-      <c r="T4" s="7" t="str">
+      <c r="T4" s="3" t="str">
         <v>Groot_S</v>
       </c>
-      <c r="U4" s="7" t="str">
+      <c r="U4" s="3" t="str">
         <v>Groot_X</v>
       </c>
       <c r="V4" s="1"/>
@@ -1124,67 +1124,67 @@
       <c r="AD4" s="1"/>
     </row>
     <row r="5">
-      <c r="A5" s="6">
+      <c r="A5" s="4">
         <v>2</v>
       </c>
-      <c r="B5" s="7" t="str">
+      <c r="B5" s="3" t="str">
         <v>BuBoom</v>
       </c>
-      <c r="C5" s="6" t="str">
+      <c r="C5" s="4" t="str">
         <v>Inorganic</v>
       </c>
-      <c r="D5" s="6" t="str">
+      <c r="D5" s="4" t="str">
         <v>A Balloonian who changes color according to its emotional state.</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="4">
         <v>2</v>
       </c>
-      <c r="F5" s="8" t="str">
+      <c r="F5" s="5" t="str">
         <v>2|6|10</v>
       </c>
-      <c r="G5" s="8">
+      <c r="G5" s="5">
         <v>3</v>
       </c>
-      <c r="H5" s="7" t="str">
+      <c r="H5" s="3" t="str">
         <v>Is that strange fur on your head actually hair?</v>
       </c>
-      <c r="I5" s="7" t="str">
+      <c r="I5" s="3" t="str">
         <v>Hair</v>
       </c>
-      <c r="J5" s="7" t="str">
+      <c r="J5" s="3" t="str">
         <v>BuBoom_prefab_1</v>
       </c>
-      <c r="K5" s="7" t="str">
+      <c r="K5" s="3" t="str">
         <v>Why is your heart so huge？</v>
       </c>
-      <c r="L5" s="7" t="str">
+      <c r="L5" s="3" t="str">
         <v>Heart</v>
       </c>
-      <c r="M5" s="7" t="str">
+      <c r="M5" s="3" t="str">
         <v>BuBoom_prefab_2</v>
       </c>
-      <c r="N5" s="7" t="str">
+      <c r="N5" s="3" t="str">
         <v>Is the air pump part of your tableware?</v>
       </c>
-      <c r="O5" s="7" t="str">
+      <c r="O5" s="3" t="str">
         <v>Air pump</v>
       </c>
-      <c r="P5" s="7" t="str">
+      <c r="P5" s="3" t="str">
         <v>BuBoom_prefab_3</v>
       </c>
-      <c r="Q5" s="9" t="str">
+      <c r="Q5" s="6" t="str">
         <v>BuBoom_glitter</v>
       </c>
-      <c r="R5" s="7" t="str">
+      <c r="R5" s="3" t="str">
         <v>BuBoom_Profile</v>
       </c>
-      <c r="S5" s="7" t="str">
+      <c r="S5" s="3" t="str">
         <v>BuBoom_appearance</v>
       </c>
-      <c r="T5" s="7" t="str">
+      <c r="T5" s="3" t="str">
         <v>BuBoom_S</v>
       </c>
-      <c r="U5" s="7" t="str">
+      <c r="U5" s="3" t="str">
         <v>BuBoom_X</v>
       </c>
       <c r="V5" s="1"/>
@@ -1198,67 +1198,67 @@
       <c r="AD5" s="1"/>
     </row>
     <row r="6">
-      <c r="A6" s="6">
+      <c r="A6" s="4">
         <v>3</v>
       </c>
-      <c r="B6" s="7" t="str">
+      <c r="B6" s="3" t="str">
         <v>Bank</v>
       </c>
-      <c r="C6" s="6" t="str">
+      <c r="C6" s="4" t="str">
         <v>Urban Legend</v>
       </c>
-      <c r="D6" s="6" t="str">
+      <c r="D6" s="4" t="str">
         <v>An eerie Mothman-like entity born from urban legends on Fajnara. In truth, it belongs to the dominant species of the planet Frattwizz.</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="4">
         <v>3</v>
       </c>
-      <c r="F6" s="8" t="str">
+      <c r="F6" s="5" t="str">
         <v>5|3|9</v>
       </c>
-      <c r="G6" s="13" t="str">
+      <c r="G6" s="14" t="str">
         <v>4|5|6</v>
       </c>
-      <c r="H6" s="7" t="str">
+      <c r="H6" s="3" t="str">
         <v>Where did those red marks on your feet come from?</v>
       </c>
-      <c r="I6" s="7" t="str">
+      <c r="I6" s="3" t="str">
         <v>Ankle</v>
       </c>
-      <c r="J6" s="7" t="str">
+      <c r="J6" s="3" t="str">
         <v>Bank_prefab_1</v>
       </c>
-      <c r="K6" s="7" t="str">
+      <c r="K6" s="3" t="str">
         <v>How did you get the gunshot wound?</v>
       </c>
-      <c r="L6" s="7" t="str">
+      <c r="L6" s="3" t="str">
         <v>Shrapnel</v>
       </c>
-      <c r="M6" s="7" t="str">
+      <c r="M6" s="3" t="str">
         <v>Bank_prefab_2</v>
       </c>
-      <c r="N6" s="7" t="str">
+      <c r="N6" s="3" t="str">
         <v>Are you a Christian?</v>
       </c>
-      <c r="O6" s="7" t="str">
+      <c r="O6" s="3" t="str">
         <v>Cross</v>
       </c>
-      <c r="P6" s="7" t="str">
+      <c r="P6" s="3" t="str">
         <v>Bank_prefab_3</v>
       </c>
-      <c r="Q6" s="14" t="str">
+      <c r="Q6" s="15" t="str">
         <v>Bank_glitter</v>
       </c>
-      <c r="R6" s="7" t="str">
+      <c r="R6" s="3" t="str">
         <v>Bank_Profile</v>
       </c>
-      <c r="S6" s="7" t="str">
+      <c r="S6" s="3" t="str">
         <v>Bank_appearance</v>
       </c>
-      <c r="T6" s="7" t="str">
+      <c r="T6" s="3" t="str">
         <v>Bank_S</v>
       </c>
-      <c r="U6" s="7" t="str">
+      <c r="U6" s="3" t="str">
         <v>Bank_X</v>
       </c>
       <c r="V6" s="1"/>
@@ -1272,67 +1272,67 @@
       <c r="AD6" s="1"/>
     </row>
     <row r="7">
-      <c r="A7" s="6">
+      <c r="A7" s="4">
         <v>4</v>
       </c>
-      <c r="B7" s="7" t="str">
+      <c r="B7" s="3" t="str">
         <v>G-007</v>
       </c>
-      <c r="C7" s="6" t="str">
+      <c r="C7" s="4" t="str">
         <v>Ferro</v>
       </c>
-      <c r="D7" s="6" t="str">
+      <c r="D7" s="4" t="str">
         <v>A satellite signal detection model. It was once the most common robot type used in interstellar exploration.</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="4">
         <v>4</v>
       </c>
-      <c r="F7" s="8" t="str">
+      <c r="F7" s="5" t="str">
         <v>2|4|7</v>
       </c>
-      <c r="G7" s="8" t="str">
+      <c r="G7" s="5" t="str">
         <v>7|8</v>
       </c>
-      <c r="H7" s="7" t="str">
+      <c r="H7" s="3" t="str">
         <v>Are you sure you can communicate with your coworkers?</v>
       </c>
-      <c r="I7" s="7" t="str">
+      <c r="I7" s="3" t="str">
         <v>Garbage characters</v>
       </c>
-      <c r="J7" s="7" t="str">
+      <c r="J7" s="3" t="str">
         <v>G-007_prefab_1</v>
       </c>
-      <c r="K7" s="7" t="str">
+      <c r="K7" s="3" t="str">
         <v>Can you still work?</v>
       </c>
-      <c r="L7" s="7" t="str">
+      <c r="L7" s="3" t="str">
         <v>Wires</v>
       </c>
-      <c r="M7" s="7" t="str">
+      <c r="M7" s="3" t="str">
         <v>G-007_prefab_2</v>
       </c>
-      <c r="N7" s="7" t="str">
+      <c r="N7" s="3" t="str">
         <v>Are you looking for a home?</v>
       </c>
-      <c r="O7" s="7" t="str">
+      <c r="O7" s="3" t="str">
         <v>ID badge</v>
       </c>
-      <c r="P7" s="7" t="str">
+      <c r="P7" s="3" t="str">
         <v>G-007_prefab_3</v>
       </c>
-      <c r="Q7" s="14" t="str">
+      <c r="Q7" s="15" t="str">
         <v>G-007_glitter</v>
       </c>
-      <c r="R7" s="7" t="str">
+      <c r="R7" s="3" t="str">
         <v>G-007_Profile</v>
       </c>
-      <c r="S7" s="7" t="str">
+      <c r="S7" s="3" t="str">
         <v>G-007_appearance</v>
       </c>
-      <c r="T7" s="7" t="str">
+      <c r="T7" s="3" t="str">
         <v>G-007_S</v>
       </c>
-      <c r="U7" s="7" t="str">
+      <c r="U7" s="3" t="str">
         <v>G-007_X</v>
       </c>
       <c r="V7" s="1"/>
@@ -1346,67 +1346,67 @@
       <c r="AD7" s="1"/>
     </row>
     <row r="8">
-      <c r="A8" s="6">
+      <c r="A8" s="4">
         <v>5</v>
       </c>
-      <c r="B8" s="7" t="str">
+      <c r="B8" s="3" t="str">
         <v>Ivy-chan</v>
       </c>
-      <c r="C8" s="6" t="str">
+      <c r="C8" s="4" t="str">
         <v>Beast</v>
       </c>
-      <c r="D8" s="6" t="str">
+      <c r="D8" s="4" t="str">
         <v>A cute little vine critter that loves snuggling up to furry creatures and climbing all over them.</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="4">
         <v>5</v>
       </c>
-      <c r="F8" s="8" t="str">
+      <c r="F8" s="5" t="str">
         <v>8|10|5</v>
       </c>
-      <c r="G8" s="13" t="str">
+      <c r="G8" s="14" t="str">
         <v>9|10|11|12</v>
       </c>
-      <c r="H8" s="7" t="str">
+      <c r="H8" s="3" t="str">
         <v>Are those lines your face?</v>
       </c>
-      <c r="I8" s="7" t="str">
+      <c r="I8" s="3" t="str">
         <v>Facial features</v>
       </c>
-      <c r="J8" s="7" t="str">
+      <c r="J8" s="3" t="str">
         <v>Ivy-chan_prefab_1</v>
       </c>
-      <c r="K8" s="7" t="str">
+      <c r="K8" s="3" t="str">
         <v>Why are there so many bone fragments in your body?</v>
       </c>
-      <c r="L8" s="7" t="str">
+      <c r="L8" s="3" t="str">
         <v>Bone fragments</v>
       </c>
-      <c r="M8" s="7" t="str">
+      <c r="M8" s="3" t="str">
         <v>Ivy-chan_prefab_2</v>
       </c>
-      <c r="N8" s="7" t="str">
+      <c r="N8" s="3" t="str">
         <v>Why do you carry so many... collectibles?</v>
       </c>
-      <c r="O8" s="7" t="str">
+      <c r="O8" s="3" t="str">
         <v>Residues</v>
       </c>
-      <c r="P8" s="7" t="str">
+      <c r="P8" s="3" t="str">
         <v>Ivy-chan_prefab_3</v>
       </c>
-      <c r="Q8" s="14" t="str">
+      <c r="Q8" s="15" t="str">
         <v>Ivy-chan_glitter</v>
       </c>
-      <c r="R8" s="7" t="str">
+      <c r="R8" s="3" t="str">
         <v>Ivy-chan_Profile</v>
       </c>
-      <c r="S8" s="7" t="str">
+      <c r="S8" s="3" t="str">
         <v>Ivy-chan_appearance</v>
       </c>
-      <c r="T8" s="7" t="str">
+      <c r="T8" s="3" t="str">
         <v>Ivy-chan_S</v>
       </c>
-      <c r="U8" s="7" t="str">
+      <c r="U8" s="3" t="str">
         <v>Ivy-chan_X</v>
       </c>
       <c r="V8" s="1"/>
@@ -1614,9 +1614,9 @@
     <row r="15">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
-      <c r="C15" s="15"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
@@ -7626,13 +7626,13 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="str">
+      <c r="A1" s="13" t="str">
         <v>ItemId</v>
       </c>
-      <c r="B1" s="3" t="str">
+      <c r="B1" s="13" t="str">
         <v>ItemName</v>
       </c>
-      <c r="C1" s="3" t="str">
+      <c r="C1" s="13" t="str">
         <v>Desc</v>
       </c>
       <c r="D1" s="17" t="str">
@@ -7653,13 +7653,13 @@
       <c r="Q1" s="17"/>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="str">
+      <c r="A2" s="13" t="str">
         <v>int</v>
       </c>
-      <c r="B2" s="3" t="str">
+      <c r="B2" s="13" t="str">
         <v>string</v>
       </c>
-      <c r="C2" s="3" t="str">
+      <c r="C2" s="13" t="str">
         <v>string</v>
       </c>
       <c r="D2" s="17" t="str">
@@ -7680,13 +7680,13 @@
       <c r="Q2" s="17"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="str">
+      <c r="A3" s="13" t="str">
         <v>Unique ID</v>
       </c>
-      <c r="B3" s="3" t="str">
+      <c r="B3" s="13" t="str">
         <v>Prop Name</v>
       </c>
-      <c r="C3" s="3" t="str">
+      <c r="C3" s="13" t="str">
         <v>Description of the item</v>
       </c>
       <c r="D3" s="17" t="str">
@@ -7707,16 +7707,16 @@
       <c r="Q3" s="17"/>
     </row>
     <row r="4">
-      <c r="A4" s="8">
+      <c r="A4" s="5">
         <v>1</v>
       </c>
-      <c r="B4" s="7" t="str">
+      <c r="B4" s="3" t="str">
         <v>Kettle</v>
       </c>
-      <c r="C4" s="8" t="str">
+      <c r="C4" s="5" t="str">
         <v>A cute mini hovering kettle that automatically waters nearby plants.</v>
       </c>
-      <c r="D4" s="7" t="str">
+      <c r="D4" s="3" t="str">
         <v>Kettle_icon</v>
       </c>
       <c r="E4" s="16"/>
@@ -7734,16 +7734,16 @@
       <c r="Q4" s="16"/>
     </row>
     <row r="5">
-      <c r="A5" s="8">
+      <c r="A5" s="5">
         <v>2</v>
       </c>
-      <c r="B5" s="8" t="str">
+      <c r="B5" s="5" t="str">
         <v>Cup of Soil</v>
       </c>
-      <c r="C5" s="8" t="str">
+      <c r="C5" s="5" t="str">
         <v>Black soil brought from Earth.</v>
       </c>
-      <c r="D5" s="8" t="str">
+      <c r="D5" s="5" t="str">
         <v>CupofSoil_icon</v>
       </c>
       <c r="E5" s="16"/>
@@ -7761,16 +7761,16 @@
       <c r="Q5" s="16"/>
     </row>
     <row r="6">
-      <c r="A6" s="8">
+      <c r="A6" s="5">
         <v>3</v>
       </c>
-      <c r="B6" s="7" t="str">
+      <c r="B6" s="3" t="str">
         <v>Air Pump</v>
       </c>
-      <c r="C6" s="8" t="str">
+      <c r="C6" s="5" t="str">
         <v>Everyone on Balloon Planet has one.</v>
       </c>
-      <c r="D6" s="7" t="str">
+      <c r="D6" s="3" t="str">
         <v>AirPump_icon</v>
       </c>
       <c r="E6" s="16"/>
@@ -7788,16 +7788,16 @@
       <c r="Q6" s="16"/>
     </row>
     <row r="7">
-      <c r="A7" s="8">
+      <c r="A7" s="5">
         <v>4</v>
       </c>
-      <c r="B7" s="7" t="str">
+      <c r="B7" s="3" t="str">
         <v>Electronic Shackles</v>
       </c>
-      <c r="C7" s="8" t="str">
+      <c r="C7" s="5" t="str">
         <v>The screen displays "Fugitive…". Code: 2002.</v>
       </c>
-      <c r="D7" s="7" t="str">
+      <c r="D7" s="3" t="str">
         <v>ElectronicShackles_icon</v>
       </c>
       <c r="E7" s="16"/>
@@ -7815,16 +7815,16 @@
       <c r="Q7" s="16"/>
     </row>
     <row r="8">
-      <c r="A8" s="8">
+      <c r="A8" s="5">
         <v>5</v>
       </c>
-      <c r="B8" s="7" t="str">
+      <c r="B8" s="3" t="str">
         <v>Cash</v>
       </c>
-      <c r="C8" s="8" t="str">
+      <c r="C8" s="5" t="str">
         <v>A roll of banknotes that seem to be exclusive tokens usable only in a certain district.</v>
       </c>
-      <c r="D8" s="7" t="str">
+      <c r="D8" s="3" t="str">
         <v>Cash_icon</v>
       </c>
       <c r="E8" s="16"/>
@@ -7842,16 +7842,16 @@
       <c r="Q8" s="16"/>
     </row>
     <row r="9">
-      <c r="A9" s="8">
+      <c r="A9" s="5">
         <v>6</v>
       </c>
-      <c r="B9" s="7" t="str">
+      <c r="B9" s="3" t="str">
         <v>Metal Cross</v>
       </c>
-      <c r="C9" s="8" t="str">
+      <c r="C9" s="5" t="str">
         <v>A faith item obtained from a visitor during prison visitation. It can be unscrewed, revealing a tiny lock-picking tool inside.</v>
       </c>
-      <c r="D9" s="7" t="str">
+      <c r="D9" s="3" t="str">
         <v>MetalCross_icon</v>
       </c>
       <c r="E9" s="16"/>
@@ -7869,16 +7869,16 @@
       <c r="Q9" s="16"/>
     </row>
     <row r="10">
-      <c r="A10" s="8">
+      <c r="A10" s="5">
         <v>7</v>
       </c>
-      <c r="B10" s="7" t="str">
+      <c r="B10" s="3" t="str">
         <v>Spare Battery</v>
       </c>
-      <c r="C10" s="8" t="str">
+      <c r="C10" s="5" t="str">
         <v>Battery power has been completely drained…</v>
       </c>
-      <c r="D10" s="7" t="str">
+      <c r="D10" s="3" t="str">
         <v>SpareBattery_icon</v>
       </c>
       <c r="E10" s="16"/>
@@ -7896,16 +7896,16 @@
       <c r="Q10" s="16"/>
     </row>
     <row r="11">
-      <c r="A11" s="8">
+      <c r="A11" s="5">
         <v>8</v>
       </c>
-      <c r="B11" s="8" t="str">
+      <c r="B11" s="5" t="str">
         <v>ID Badge</v>
       </c>
-      <c r="C11" s="8" t="str">
+      <c r="C11" s="5" t="str">
         <v>Embedded in the palm of G-007's hand. In the bottom right corner, a tiny engraving reads: "where is the home".</v>
       </c>
-      <c r="D11" s="8" t="str">
+      <c r="D11" s="5" t="str">
         <v>IDBadge_icon</v>
       </c>
       <c r="E11" s="16"/>
@@ -7923,16 +7923,16 @@
       <c r="Q11" s="16"/>
     </row>
     <row r="12">
-      <c r="A12" s="8">
+      <c r="A12" s="5">
         <v>9</v>
       </c>
-      <c r="B12" s="8" t="str">
+      <c r="B12" s="5" t="str">
         <v>Mantis Arm</v>
       </c>
-      <c r="C12" s="8" t="str">
+      <c r="C12" s="5" t="str">
         <v>A green hollow scythe-like arm, perfectly shaped but covered in corroded pitted holes.</v>
       </c>
-      <c r="D12" s="8" t="str">
+      <c r="D12" s="5" t="str">
         <v>MantisArm_icon</v>
       </c>
       <c r="E12" s="16"/>
@@ -7950,16 +7950,16 @@
       <c r="Q12" s="16"/>
     </row>
     <row r="13">
-      <c r="A13" s="8">
+      <c r="A13" s="5">
         <v>10</v>
       </c>
-      <c r="B13" s="8" t="str">
+      <c r="B13" s="5" t="str">
         <v>Black Unknown Substance</v>
       </c>
-      <c r="C13" s="8" t="str">
+      <c r="C13" s="5" t="str">
         <v>Upon closer inspection, insects can be seen struggling and writhing inside the viscous slime.</v>
       </c>
-      <c r="D13" s="8" t="str">
+      <c r="D13" s="5" t="str">
         <v>BlackUnknownSubstance_icon</v>
       </c>
       <c r="E13" s="16"/>
@@ -7977,16 +7977,16 @@
       <c r="Q13" s="16"/>
     </row>
     <row r="14">
-      <c r="A14" s="8">
+      <c r="A14" s="5">
         <v>11</v>
       </c>
-      <c r="B14" s="9" t="str">
+      <c r="B14" s="6" t="str">
         <v>Flesh Lump</v>
       </c>
-      <c r="C14" s="7" t="str">
+      <c r="C14" s="3" t="str">
         <v>In a half-digested state, covered with pale yellow mucus.</v>
       </c>
-      <c r="D14" s="9" t="str">
+      <c r="D14" s="6" t="str">
         <v>FleshLump_icon</v>
       </c>
       <c r="E14" s="16"/>
@@ -8004,16 +8004,16 @@
       <c r="Q14" s="16"/>
     </row>
     <row r="15">
-      <c r="A15" s="8">
+      <c r="A15" s="5">
         <v>12</v>
       </c>
-      <c r="B15" s="9" t="str">
+      <c r="B15" s="6" t="str">
         <v>Crimson Snake Skin</v>
       </c>
-      <c r="C15" s="9" t="str">
+      <c r="C15" s="6" t="str">
         <v>Tightly wrapped around the vines, heavily fragmented and torn.</v>
       </c>
-      <c r="D15" s="9" t="str">
+      <c r="D15" s="6" t="str">
         <v>CrimsonSnakeSkin_icon</v>
       </c>
       <c r="E15" s="16"/>
@@ -11565,276 +11565,276 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="str">
+      <c r="A1" s="11" t="str">
         <v>Planet_Id</v>
       </c>
-      <c r="B1" s="4" t="str">
+      <c r="B1" s="11" t="str">
         <v>Planet</v>
       </c>
-      <c r="C1" s="2" t="str">
+      <c r="C1" s="8" t="str">
         <v>Planet_Desc</v>
       </c>
-      <c r="D1" s="2" t="str">
+      <c r="D1" s="8" t="str">
         <v>Planet_need</v>
       </c>
-      <c r="E1" s="2" t="str">
+      <c r="E1" s="8" t="str">
         <v>Planet_icon</v>
       </c>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="11"/>
-      <c r="J1" s="11"/>
-      <c r="K1" s="11"/>
-      <c r="L1" s="11"/>
-      <c r="M1" s="11"/>
-      <c r="N1" s="11"/>
-      <c r="O1" s="11"/>
-      <c r="P1" s="11"/>
-      <c r="Q1" s="11"/>
-      <c r="R1" s="11"/>
-      <c r="S1" s="11"/>
-      <c r="T1" s="11"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+      <c r="M1" s="10"/>
+      <c r="N1" s="10"/>
+      <c r="O1" s="10"/>
+      <c r="P1" s="10"/>
+      <c r="Q1" s="10"/>
+      <c r="R1" s="10"/>
+      <c r="S1" s="10"/>
+      <c r="T1" s="10"/>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="str">
+      <c r="A2" s="11" t="str">
         <v>int</v>
       </c>
-      <c r="B2" s="4" t="str">
+      <c r="B2" s="11" t="str">
         <v>string</v>
       </c>
-      <c r="C2" s="2" t="str">
+      <c r="C2" s="8" t="str">
         <v>string</v>
       </c>
-      <c r="D2" s="2" t="str">
+      <c r="D2" s="8" t="str">
         <v>string</v>
       </c>
-      <c r="E2" s="2" t="str">
+      <c r="E2" s="8" t="str">
         <v>string</v>
       </c>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="11"/>
-      <c r="J2" s="11"/>
-      <c r="K2" s="11"/>
-      <c r="L2" s="11"/>
-      <c r="M2" s="11"/>
-      <c r="N2" s="11"/>
-      <c r="O2" s="11"/>
-      <c r="P2" s="11"/>
-      <c r="Q2" s="11"/>
-      <c r="R2" s="11"/>
-      <c r="S2" s="11"/>
-      <c r="T2" s="11"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
+      <c r="N2" s="10"/>
+      <c r="O2" s="10"/>
+      <c r="P2" s="10"/>
+      <c r="Q2" s="10"/>
+      <c r="R2" s="10"/>
+      <c r="S2" s="10"/>
+      <c r="T2" s="10"/>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="str">
+      <c r="A3" s="11" t="str">
         <v>唯一id</v>
       </c>
-      <c r="B3" s="4" t="str">
+      <c r="B3" s="11" t="str">
         <v>星球的名字</v>
       </c>
-      <c r="C3" s="2" t="str">
+      <c r="C3" s="8" t="str">
         <v>星球描述文本</v>
       </c>
-      <c r="D3" s="2" t="str">
+      <c r="D3" s="8" t="str">
         <v>星球需求文本</v>
       </c>
-      <c r="E3" s="2" t="str">
+      <c r="E3" s="8" t="str">
         <v>星球icon</v>
       </c>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11"/>
-      <c r="H3" s="11"/>
-      <c r="I3" s="11"/>
-      <c r="J3" s="11"/>
-      <c r="K3" s="11"/>
-      <c r="L3" s="11"/>
-      <c r="M3" s="11"/>
-      <c r="N3" s="11"/>
-      <c r="O3" s="11"/>
-      <c r="P3" s="11"/>
-      <c r="Q3" s="11"/>
-      <c r="R3" s="11"/>
-      <c r="S3" s="11"/>
-      <c r="T3" s="11"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="10"/>
+      <c r="N3" s="10"/>
+      <c r="O3" s="10"/>
+      <c r="P3" s="10"/>
+      <c r="Q3" s="10"/>
+      <c r="R3" s="10"/>
+      <c r="S3" s="10"/>
+      <c r="T3" s="10"/>
     </row>
     <row r="4">
-      <c r="A4" s="14">
+      <c r="A4" s="15">
         <v>1</v>
       </c>
-      <c r="B4" s="14" t="str">
+      <c r="B4" s="15" t="str">
         <v>Budya</v>
       </c>
-      <c r="C4" s="14" t="str">
+      <c r="C4" s="15" t="str">
         <v>An extraterrestrial paradise born from pure, innocent hearts. A world composed of harmless flora and fauna.</v>
       </c>
-      <c r="D4" s="14" t="str">
+      <c r="D4" s="15" t="str">
         <v>Everyone is welcome to join OVO!</v>
       </c>
-      <c r="E4" s="14" t="str">
+      <c r="E4" s="15" t="str">
         <v>Budya_icon</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="14">
+      <c r="A5" s="15">
         <v>2</v>
       </c>
-      <c r="B5" s="14" t="str">
+      <c r="B5" s="15" t="str">
         <v>Tonis</v>
       </c>
-      <c r="C5" s="14" t="str">
+      <c r="C5" s="15" t="str">
         <v>Highly commercialized. The designated supplier for the Interstellar Alliance.</v>
       </c>
-      <c r="D5" s="14" t="str">
+      <c r="D5" s="15" t="str">
         <v>Hiring hair stylists. Speak with your hands, come quickly!</v>
       </c>
-      <c r="E5" s="14" t="str">
+      <c r="E5" s="15" t="str">
         <v>Tonis_icon</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="14">
+      <c r="A6" s="15">
         <v>3</v>
       </c>
-      <c r="B6" s="14" t="str">
+      <c r="B6" s="15" t="str">
         <v>Shawshank</v>
       </c>
-      <c r="C6" s="14" t="str">
+      <c r="C6" s="15" t="str">
         <v>Over 80% of the planet is ocean. The only landmass hosts the galaxy's most heavily guarded maximum-security prison.</v>
       </c>
-      <c r="D6" s="14" t="str">
+      <c r="D6" s="15" t="str">
         <v>Urgent need for 10 maintenance workers.
 "The highest bounty for an escaped prisoner is 503,333…"</v>
       </c>
-      <c r="E6" s="14" t="str">
+      <c r="E6" s="15" t="str">
         <v>Shawshank_icon</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="14">
+      <c r="A7" s="15">
         <v>4</v>
       </c>
-      <c r="B7" s="14" t="str">
+      <c r="B7" s="15" t="str">
         <v>Screw</v>
       </c>
-      <c r="C7" s="14" t="str">
+      <c r="C7" s="15" t="str">
         <v>A collective of intelligent mechanical spirals. The entire planet has been transformed into a massive starship.</v>
       </c>
-      <c r="D7" s="14" t="str">
+      <c r="D7" s="15" t="str">
         <v>Hiring crew members.
 Old exploration-type robots welcome. Only the core needs to be intact.
 The ship has ample space and no wear-and-tear issues.</v>
       </c>
-      <c r="E7" s="14" t="str">
+      <c r="E7" s="15" t="str">
         <v>Screw_icon</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="14">
+      <c r="A8" s="15">
         <v>5</v>
       </c>
-      <c r="B8" s="14" t="str">
+      <c r="B8" s="15" t="str">
         <v>Arrakis</v>
       </c>
-      <c r="C8" s="14" t="str">
+      <c r="C8" s="15" t="str">
         <v>Once rich with immense energy sources, now a lawless paradise for outlaws after drying up.</v>
       </c>
-      <c r="D8" s="14" t="str">
+      <c r="D8" s="15" t="str">
         <v>It's a Sicilian message. It means Luca Brasi sleeps with the fishes.Send it and you take the money.</v>
       </c>
-      <c r="E8" s="14" t="str">
+      <c r="E8" s="15" t="str">
         <v>Arrakis_icon</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="14">
+      <c r="A9" s="15">
         <v>6</v>
       </c>
-      <c r="B9" s="14" t="str">
+      <c r="B9" s="15" t="str">
         <v>Lost Eden</v>
       </c>
-      <c r="C9" s="14" t="str">
+      <c r="C9" s="15" t="str">
         <v>A garden of Eden-like bliss. If you can imagine it, you can have endless joy here.</v>
       </c>
-      <c r="D9" s="14" t="str">
+      <c r="D9" s="15" t="str">
         <v>Work? No, come play. Your only responsibility is to make yourself happy -- and feel free to tell others how to be even happier.</v>
       </c>
-      <c r="E9" s="14" t="str">
+      <c r="E9" s="15" t="str">
         <v>LostEden_icon</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="14">
+      <c r="A10" s="15">
         <v>7</v>
       </c>
-      <c r="B10" s="14" t="str">
+      <c r="B10" s="15" t="str">
         <v>Jelly</v>
       </c>
-      <c r="C10" s="14" t="str">
+      <c r="C10" s="15" t="str">
         <v>The planet's surface is covered in gelatinous material. The favorite amusement park destination for interstellar families with children.</v>
       </c>
-      <c r="D10" s="14" t="str">
+      <c r="D10" s="15" t="str">
         <v>Hiring a Jelly Pit Rescue Assistant. Rescue stuck kids, keep them smiling, stay cheerful. Free park access included.</v>
       </c>
-      <c r="E10" s="14" t="str">
+      <c r="E10" s="15" t="str">
         <v>Jelly_icon</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="14">
+      <c r="A11" s="15">
         <v>8</v>
       </c>
-      <c r="B11" s="14" t="str">
+      <c r="B11" s="15" t="str">
         <v>Cinnabar Eye</v>
       </c>
-      <c r="C11" s="14" t="str">
+      <c r="C11" s="15" t="str">
         <v>The atmosphere consists of hydrogen and helium. The largest gas giant in the Kartos Star System.</v>
       </c>
-      <c r="D11" s="14" t="str">
+      <c r="D11" s="15" t="str">
         <v>Position: Lead Scout
 Duties: Explore uncharted areas and collect resource and risk data.
 Compensation: Paid per validated report. Reports are archived only; retrieval of personnel is not guaranteed.</v>
       </c>
-      <c r="E11" s="14" t="str">
+      <c r="E11" s="15" t="str">
         <v>CinnabarEye_icon</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="14">
+      <c r="A12" s="15">
         <v>9</v>
       </c>
-      <c r="B12" s="14" t="str">
+      <c r="B12" s="15" t="str">
         <v>Surukan</v>
       </c>
-      <c r="C12" s="14" t="str">
+      <c r="C12" s="15" t="str">
         <v>A realm of serene silence. Every citizen focuses solely on themselves.</v>
       </c>
-      <c r="D12" s="14" t="str">
+      <c r="D12" s="15" t="str">
         <v>Position: Boundary Keeper
 Duties: Protect personal boundaries
 Requirements: Fair
 </v>
       </c>
-      <c r="E12" s="14" t="str">
+      <c r="E12" s="15" t="str">
         <v>Surukan_icon</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="14">
+      <c r="A13" s="15">
         <v>10</v>
       </c>
-      <c r="B13" s="14" t="str">
+      <c r="B13" s="15" t="str">
         <v>Tarasus</v>
       </c>
-      <c r="C13" s="14" t="str">
+      <c r="C13" s="15" t="str">
         <v>An ocean of trees. Countless roots intertwine and fuse together, united as one.</v>
       </c>
-      <c r="D13" s="14" t="str">
+      <c r="D13" s="15" t="str">
         <v>Roots entwined with roots - though they occasionally tangle and twist. The old village chief has stiff legs and speaks slowly. We're short a translator who can listen to both sides of the tree-root conversations.</v>
       </c>
-      <c r="E13" s="14" t="str">
+      <c r="E13" s="15" t="str">
         <v>Tarasus_icon</v>
       </c>
     </row>
@@ -12419,65 +12419,65 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="str">
+      <c r="A1" s="13" t="str">
         <v>Remarks</v>
       </c>
-      <c r="B1" s="3" t="str">
+      <c r="B1" s="13" t="str">
         <v>DialogueId</v>
       </c>
-      <c r="C1" s="3" t="str">
+      <c r="C1" s="13" t="str">
         <v>Text</v>
       </c>
-      <c r="D1" s="3" t="str">
+      <c r="D1" s="13" t="str">
         <v>next</v>
       </c>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="11"/>
-      <c r="J1" s="11"/>
-      <c r="K1" s="11"/>
-      <c r="L1" s="11"/>
-      <c r="M1" s="11"/>
-      <c r="N1" s="11"/>
-      <c r="O1" s="11"/>
-      <c r="P1" s="11"/>
-      <c r="Q1" s="11"/>
-      <c r="R1" s="11"/>
-      <c r="S1" s="11"/>
-      <c r="T1" s="11"/>
-      <c r="U1" s="11"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+      <c r="M1" s="10"/>
+      <c r="N1" s="10"/>
+      <c r="O1" s="10"/>
+      <c r="P1" s="10"/>
+      <c r="Q1" s="10"/>
+      <c r="R1" s="10"/>
+      <c r="S1" s="10"/>
+      <c r="T1" s="10"/>
+      <c r="U1" s="10"/>
     </row>
     <row r="2">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3" t="str">
+      <c r="A2" s="13"/>
+      <c r="B2" s="13" t="str">
         <v>int</v>
       </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="11"/>
-      <c r="J2" s="11"/>
-      <c r="K2" s="11"/>
-      <c r="L2" s="11"/>
-      <c r="M2" s="11"/>
-      <c r="N2" s="11"/>
-      <c r="O2" s="11"/>
-      <c r="P2" s="11"/>
-      <c r="Q2" s="11"/>
-      <c r="R2" s="11"/>
-      <c r="S2" s="11"/>
-      <c r="T2" s="11"/>
-      <c r="U2" s="11"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
+      <c r="N2" s="10"/>
+      <c r="O2" s="10"/>
+      <c r="P2" s="10"/>
+      <c r="Q2" s="10"/>
+      <c r="R2" s="10"/>
+      <c r="S2" s="10"/>
+      <c r="T2" s="10"/>
+      <c r="U2" s="10"/>
     </row>
     <row r="3">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3" t="str">
+      <c r="A3" s="13"/>
+      <c r="B3" s="13"/>
+      <c r="C3" s="13" t="str">
         <v>Name: Speaker Content
 Special Speaker Chice
 "Choice
@@ -12485,150 +12485,150 @@
 Option 2 text content | 0
 Text content of Option 3 | 0 represents end</v>
       </c>
-      <c r="D3" s="3"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11"/>
-      <c r="H3" s="11"/>
-      <c r="I3" s="11"/>
-      <c r="J3" s="11"/>
-      <c r="K3" s="11"/>
-      <c r="L3" s="11"/>
-      <c r="M3" s="11"/>
-      <c r="N3" s="11"/>
-      <c r="O3" s="11"/>
-      <c r="P3" s="11">
+      <c r="D3" s="13"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="10"/>
+      <c r="N3" s="10"/>
+      <c r="O3" s="10"/>
+      <c r="P3" s="10">
         <v>5</v>
       </c>
-      <c r="Q3" s="11"/>
-      <c r="R3" s="11"/>
-      <c r="S3" s="11"/>
-      <c r="T3" s="11"/>
-      <c r="U3" s="11"/>
+      <c r="Q3" s="10"/>
+      <c r="R3" s="10"/>
+      <c r="S3" s="10"/>
+      <c r="T3" s="10"/>
+      <c r="U3" s="10"/>
     </row>
     <row customHeight="true" ht="28" r="4">
-      <c r="A4" s="19" t="str">
+      <c r="A4" s="24" t="str">
         <v>Performance 1 Opening</v>
       </c>
-      <c r="B4" s="19"/>
-      <c r="C4" s="19"/>
-      <c r="D4" s="19"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="18"/>
-      <c r="H4" s="18"/>
-      <c r="I4" s="18"/>
-      <c r="J4" s="18"/>
-      <c r="K4" s="18"/>
-      <c r="L4" s="18"/>
-      <c r="M4" s="18"/>
-      <c r="N4" s="18"/>
-      <c r="O4" s="18"/>
-      <c r="P4" s="18"/>
-      <c r="Q4" s="18"/>
-      <c r="R4" s="18"/>
-      <c r="S4" s="18"/>
-      <c r="T4" s="18"/>
-      <c r="U4" s="18"/>
+      <c r="B4" s="24"/>
+      <c r="C4" s="24"/>
+      <c r="D4" s="24"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="20"/>
+      <c r="H4" s="20"/>
+      <c r="I4" s="20"/>
+      <c r="J4" s="20"/>
+      <c r="K4" s="20"/>
+      <c r="L4" s="20"/>
+      <c r="M4" s="20"/>
+      <c r="N4" s="20"/>
+      <c r="O4" s="20"/>
+      <c r="P4" s="20"/>
+      <c r="Q4" s="20"/>
+      <c r="R4" s="20"/>
+      <c r="S4" s="20"/>
+      <c r="T4" s="20"/>
+      <c r="U4" s="20"/>
     </row>
     <row customHeight="true" ht="86" r="5">
-      <c r="A5" s="8"/>
-      <c r="B5" s="8">
+      <c r="A5" s="5"/>
+      <c r="B5" s="5">
         <v>1</v>
       </c>
-      <c r="C5" s="8" t="str">
+      <c r="C5" s="5" t="str">
         <v>Manager: New face, huh? Come on in. Sit down, relax. No need to look so nervous. I'm the... acting manager of this Interstellar Dispatch Office for the time being.
 Manager: You ever heard of the Galactic HR Department?
 Choice
 Yes|2
 No|3</v>
       </c>
-      <c r="D5" s="8"/>
-      <c r="E5" s="15"/>
-      <c r="F5" s="15"/>
-      <c r="G5" s="15"/>
-      <c r="H5" s="15"/>
-      <c r="I5" s="15"/>
-      <c r="J5" s="15"/>
-      <c r="K5" s="15"/>
-      <c r="L5" s="15"/>
-      <c r="M5" s="15"/>
-      <c r="N5" s="15"/>
-      <c r="O5" s="15"/>
-      <c r="P5" s="15"/>
-      <c r="Q5" s="15"/>
-      <c r="R5" s="15"/>
-      <c r="S5" s="15"/>
-      <c r="T5" s="15"/>
-      <c r="U5" s="15"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2"/>
+      <c r="P5" s="2"/>
+      <c r="Q5" s="2"/>
+      <c r="R5" s="2"/>
+      <c r="S5" s="2"/>
+      <c r="T5" s="2"/>
+      <c r="U5" s="2"/>
     </row>
     <row r="6">
-      <c r="A6" s="8"/>
-      <c r="B6" s="8">
+      <c r="A6" s="5"/>
+      <c r="B6" s="5">
         <v>2</v>
       </c>
-      <c r="C6" s="8" t="str">
+      <c r="C6" s="5" t="str">
         <v>Manager: Great. Then I'll keep it short. We've had a flood of alien job seekers lately. Whole crowds of them.
 Manager: They're sick of their home planets, bored out of their skulls, and looking for somewhere new to work.</v>
       </c>
-      <c r="D6" s="8">
+      <c r="D6" s="5">
         <v>4</v>
       </c>
-      <c r="E6" s="15"/>
-      <c r="F6" s="15"/>
-      <c r="G6" s="15"/>
-      <c r="H6" s="15"/>
-      <c r="I6" s="15"/>
-      <c r="J6" s="15"/>
-      <c r="K6" s="15"/>
-      <c r="L6" s="15"/>
-      <c r="M6" s="15"/>
-      <c r="N6" s="15"/>
-      <c r="O6" s="15"/>
-      <c r="P6" s="15"/>
-      <c r="Q6" s="15"/>
-      <c r="R6" s="15"/>
-      <c r="S6" s="15"/>
-      <c r="T6" s="15"/>
-      <c r="U6" s="15"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
+      <c r="M6" s="2"/>
+      <c r="N6" s="2"/>
+      <c r="O6" s="2"/>
+      <c r="P6" s="2"/>
+      <c r="Q6" s="2"/>
+      <c r="R6" s="2"/>
+      <c r="S6" s="2"/>
+      <c r="T6" s="2"/>
+      <c r="U6" s="2"/>
     </row>
     <row r="7">
-      <c r="A7" s="8"/>
-      <c r="B7" s="8">
+      <c r="A7" s="5"/>
+      <c r="B7" s="5">
         <v>3</v>
       </c>
-      <c r="C7" s="8" t="str">
+      <c r="C7" s="5" t="str">
         <v>Manager: No worries. Honestly, they mostly just send emails.
 Manager: Long story short, alien job seekers have been pouring in lately.
 Manager:They're tired of life back home and want a fresh start. New planet, new job, same old trouble.</v>
       </c>
-      <c r="D7" s="8">
+      <c r="D7" s="5">
         <v>4</v>
       </c>
-      <c r="E7" s="15"/>
-      <c r="F7" s="15"/>
-      <c r="G7" s="15"/>
-      <c r="H7" s="15"/>
-      <c r="I7" s="15"/>
-      <c r="J7" s="15"/>
-      <c r="K7" s="15"/>
-      <c r="L7" s="15"/>
-      <c r="M7" s="15"/>
-      <c r="N7" s="15"/>
-      <c r="O7" s="15"/>
-      <c r="P7" s="15"/>
-      <c r="Q7" s="15"/>
-      <c r="R7" s="15"/>
-      <c r="S7" s="15"/>
-      <c r="T7" s="15"/>
-      <c r="U7" s="15"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
+      <c r="N7" s="2"/>
+      <c r="O7" s="2"/>
+      <c r="P7" s="2"/>
+      <c r="Q7" s="2"/>
+      <c r="R7" s="2"/>
+      <c r="S7" s="2"/>
+      <c r="T7" s="2"/>
+      <c r="U7" s="2"/>
     </row>
     <row r="8">
-      <c r="A8" s="8"/>
-      <c r="B8" s="8">
+      <c r="A8" s="5"/>
+      <c r="B8" s="5">
         <v>4</v>
       </c>
-      <c r="C8" s="8" t="str">
+      <c r="C8" s="5" t="str">
         <v>Manager: The problem is, some of them have tempers hot enough to melt steel.
 Manager: Some are dumb as asteroids.
 Manager: And some of them... well.
@@ -12639,312 +12639,403 @@
 Manager: That's the rundown. Good luck, kiddo.
 Manager: Try not to get eaten.Ciao~</v>
       </c>
-      <c r="D8" s="8"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="15"/>
-      <c r="G8" s="15"/>
-      <c r="H8" s="15"/>
-      <c r="I8" s="15"/>
-      <c r="J8" s="15"/>
-      <c r="K8" s="15"/>
-      <c r="L8" s="15"/>
-      <c r="M8" s="15"/>
-      <c r="N8" s="15"/>
-      <c r="O8" s="15"/>
-      <c r="P8" s="15"/>
-      <c r="Q8" s="15"/>
-      <c r="R8" s="15"/>
-      <c r="S8" s="15"/>
-      <c r="T8" s="15"/>
-      <c r="U8" s="15"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
+      <c r="N8" s="2"/>
+      <c r="O8" s="2"/>
+      <c r="P8" s="2"/>
+      <c r="Q8" s="2"/>
+      <c r="R8" s="2"/>
+      <c r="S8" s="2"/>
+      <c r="T8" s="2"/>
+      <c r="U8" s="2"/>
     </row>
     <row r="9">
-      <c r="A9" s="19" t="str">
+      <c r="A9" s="24" t="str">
         <v>Performance 2 Beginner's Guide</v>
       </c>
-      <c r="B9" s="19"/>
-      <c r="C9" s="19"/>
-      <c r="D9" s="19"/>
-      <c r="E9" s="18"/>
-      <c r="F9" s="18"/>
-      <c r="G9" s="18"/>
-      <c r="H9" s="18"/>
-      <c r="I9" s="18"/>
-      <c r="J9" s="18"/>
-      <c r="K9" s="18"/>
-      <c r="L9" s="18"/>
-      <c r="M9" s="18"/>
-      <c r="N9" s="18"/>
-      <c r="O9" s="18"/>
-      <c r="P9" s="18"/>
-      <c r="Q9" s="18"/>
-      <c r="R9" s="18"/>
-      <c r="S9" s="18"/>
-      <c r="T9" s="18"/>
-      <c r="U9" s="18"/>
+      <c r="B9" s="24"/>
+      <c r="C9" s="24"/>
+      <c r="D9" s="24"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="20"/>
+      <c r="G9" s="20"/>
+      <c r="H9" s="20"/>
+      <c r="I9" s="20"/>
+      <c r="J9" s="20"/>
+      <c r="K9" s="20"/>
+      <c r="L9" s="20"/>
+      <c r="M9" s="20"/>
+      <c r="N9" s="20"/>
+      <c r="O9" s="20"/>
+      <c r="P9" s="20"/>
+      <c r="Q9" s="20"/>
+      <c r="R9" s="20"/>
+      <c r="S9" s="20"/>
+      <c r="T9" s="20"/>
+      <c r="U9" s="20"/>
     </row>
     <row r="10">
-      <c r="A10" s="20"/>
-      <c r="B10" s="8">
+      <c r="A10" s="18"/>
+      <c r="B10" s="5">
         <v>16</v>
       </c>
-      <c r="C10" s="8" t="str">
+      <c r="C10" s="5" t="str">
         <v>Woofie: Hey there, rookie! I'm Woofie, your senior guide around here. Woof!
 Woofie: This right here is your workstation.
 Woofie: Any creatures needing placement will show up at the window. Woof!
 Woofie: You can check their [PROFILE] on the tablet below.
 Woofie: Use the tabs to switch screens and inspect whatever they're carrying in their [PACKAGE].</v>
       </c>
-      <c r="D10" s="8">
+      <c r="D10" s="5">
         <v>17</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="20"/>
-      <c r="B11" s="8">
+      <c r="A11" s="18"/>
+      <c r="B11" s="5">
         <v>17</v>
       </c>
-      <c r="C11" s="8" t="str">
+      <c r="C11" s="5" t="str">
         <v>Woofie: These are the scanning buttons. Woof!
 Woofie: Tap [SCAN] to check their external features, or [X-RAY] to get a look at their internal skeleton.</v>
       </c>
-      <c r="D11" s="8">
+      <c r="D11" s="5">
         <v>18</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="20"/>
-      <c r="B12" s="8">
+      <c r="A12" s="18"/>
+      <c r="B12" s="5">
         <v>18</v>
       </c>
-      <c r="C12" s="8" t="str">
+      <c r="C12" s="5" t="str">
         <v>Woofie: Now then, a proper dispatcher also needs to ask a few simple questions.
 Woofie: That's what the [ASK] button is for.
 Woofie: After that, you can review their answers in the [PROFILE] tab.
 Woofie: Oh, and one important thing-if you haven't examined them properly first, the [ASK] button won't work. Woof!</v>
       </c>
-      <c r="D12" s="8">
+      <c r="D12" s="5">
         <v>19</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="20"/>
-      <c r="B13" s="8">
+      <c r="A13" s="18"/>
+      <c r="B13" s="5">
         <v>19</v>
       </c>
-      <c r="C13" s="8" t="str">
+      <c r="C13" s="5" t="str">
         <v>Woofie: Once you think you've got them figured out, hit [DISPATCH] and choose the planet that suits them best.</v>
       </c>
-      <c r="D13" s="8">
+      <c r="D13" s="5">
         <v>20</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="20"/>
-      <c r="B14" s="8">
+      <c r="A14" s="18"/>
+      <c r="B14" s="5">
         <v>20</v>
       </c>
-      <c r="C14" s="6" t="str">
+      <c r="C14" s="4" t="str">
         <v>Woofie: I believe in you, rookie! Woof!</v>
       </c>
-      <c r="D14" s="6"/>
+      <c r="D14" s="4"/>
     </row>
     <row r="15">
-      <c r="A15" s="22" t="str">
+      <c r="A15" s="21" t="str">
         <v>Performance 3 ending</v>
       </c>
-      <c r="B15" s="23"/>
-      <c r="C15" s="23"/>
-      <c r="D15" s="23"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="18"/>
-      <c r="G15" s="18"/>
-      <c r="H15" s="18"/>
-      <c r="I15" s="18"/>
-      <c r="J15" s="18"/>
-      <c r="K15" s="18"/>
-      <c r="L15" s="18"/>
-      <c r="M15" s="18"/>
-      <c r="N15" s="18"/>
-      <c r="O15" s="18"/>
-      <c r="P15" s="18"/>
-      <c r="Q15" s="18"/>
-      <c r="R15" s="18"/>
-      <c r="S15" s="18"/>
-      <c r="T15" s="18"/>
-      <c r="U15" s="18"/>
+      <c r="B15" s="22"/>
+      <c r="C15" s="22"/>
+      <c r="D15" s="22"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="20"/>
+      <c r="G15" s="20"/>
+      <c r="H15" s="20"/>
+      <c r="I15" s="20"/>
+      <c r="J15" s="20"/>
+      <c r="K15" s="20"/>
+      <c r="L15" s="20"/>
+      <c r="M15" s="20"/>
+      <c r="N15" s="20"/>
+      <c r="O15" s="20"/>
+      <c r="P15" s="20"/>
+      <c r="Q15" s="20"/>
+      <c r="R15" s="20"/>
+      <c r="S15" s="20"/>
+      <c r="T15" s="20"/>
+      <c r="U15" s="20"/>
     </row>
     <row r="16">
-      <c r="A16" s="20"/>
-      <c r="B16" s="21">
+      <c r="A16" s="18" t="str">
+        <v>只判定正确错误两种</v>
+      </c>
+      <c r="B16" s="19">
         <v>5</v>
       </c>
-      <c r="C16" s="20" t="str">
+      <c r="C16" s="18" t="str">
         <v>Manager: Oh! Looks like you survived your first day on the job.
 Manager: Let me see that performance report...
-Manager: [n] satisfied, [n] average, [n] complaints.</v>
-      </c>
-      <c r="D16" s="20"/>
+Manager：Your dispatches have disappointed them[ n ]times and satisfied them[ n ]times!</v>
+      </c>
+      <c r="D16" s="18"/>
     </row>
     <row r="17">
-      <c r="A17" s="20" t="str">
+      <c r="A17" s="18" t="str">
         <v>(When 0 mistakes)</v>
       </c>
-      <c r="B17" s="21">
+      <c r="B17" s="19">
         <v>6</v>
       </c>
-      <c r="C17" s="21" t="str">
+      <c r="C17" s="19" t="str">
         <v>Manager: Well, well. You're sharper than you look.
 Choice
 Heh~|11
 Not bad, right?|11</v>
       </c>
-      <c r="D17" s="21"/>
+      <c r="D17" s="19"/>
     </row>
     <row r="18">
-      <c r="A18" s="20" t="str">
+      <c r="A18" s="18" t="str">
         <v>(When 1 or 2 mistakes)</v>
       </c>
-      <c r="B18" s="21">
+      <c r="B18" s="19">
         <v>7</v>
       </c>
-      <c r="C18" s="21" t="str">
+      <c r="C18" s="19" t="str">
         <v>Manager: Hm. You're taking this seriously. I like that.
 Choice
 Heh~|12
 Not bad, right?|12</v>
       </c>
-      <c r="D18" s="21"/>
+      <c r="D18" s="19"/>
     </row>
     <row r="19">
-      <c r="A19" s="20" t="str">
+      <c r="A19" s="18" t="str">
         <v>(When 3 or 4 mistakes)</v>
       </c>
-      <c r="B19" s="21">
+      <c r="B19" s="19">
         <v>8</v>
       </c>
-      <c r="C19" s="21" t="str">
+      <c r="C19" s="19" t="str">
         <v>Manager: Looks like you've still got a lot to learn.
 Choice
 Heh~|13
 Not bad, right?|13</v>
       </c>
-      <c r="D19" s="21"/>
+      <c r="D19" s="19"/>
     </row>
     <row r="20">
-      <c r="A20" s="20" t="str">
+      <c r="A20" s="18" t="str">
         <v>(When 5 mistakes)</v>
       </c>
-      <c r="B20" s="21">
+      <c r="B20" s="19">
         <v>9</v>
       </c>
-      <c r="C20" s="21" t="str">
+      <c r="C20" s="19" t="str">
         <v>Manager: Good grief. Were you making decisions with your elbows?
 Choice
 Heh~|14
 Not bad, right?|14</v>
       </c>
-      <c r="D20" s="21"/>
+      <c r="D20" s="19"/>
     </row>
     <row r="21">
-      <c r="A21" s="20"/>
-      <c r="B21" s="21">
+      <c r="A21" s="18"/>
+      <c r="B21" s="19">
         <v>11</v>
       </c>
-      <c r="C21" s="21" t="str">
+      <c r="C21" s="19" t="str">
         <v>Manager: I knew I wasn't wrong about you.
 Manager: Talented inspectors are getting harder to find these days.
 Manager: Keep this up, and you might even earn yourself a promotion to headquarters before long.</v>
       </c>
-      <c r="D21" s="21">
+      <c r="D21" s="19">
         <v>15</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="20"/>
-      <c r="B22" s="21">
+      <c r="A22" s="18"/>
+      <c r="B22" s="19">
         <v>12</v>
       </c>
-      <c r="C22" s="21" t="str">
+      <c r="C22" s="19" t="str">
         <v>Manager: Confidence is good. Keep that fire in you.
 Manager: Just don't slack off on your training.
 Manager: And ask your senior, Woofie, plenty of questions while you can.</v>
       </c>
-      <c r="D22" s="21">
+      <c r="D22" s="19">
         <v>15</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="20"/>
-      <c r="B23" s="21">
+      <c r="A23" s="18"/>
+      <c r="B23" s="19">
         <v>13</v>
       </c>
-      <c r="C23" s="21" t="str">
+      <c r="C23" s="19" t="str">
         <v>Manager: Hah. Got jokes, huh?
 Manager: Still, for a rookie to make it this far already... not bad at all.</v>
       </c>
-      <c r="D23" s="21">
+      <c r="D23" s="19">
         <v>15</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="20"/>
-      <c r="B24" s="21">
+      <c r="A24" s="18"/>
+      <c r="B24" s="19">
         <v>14</v>
       </c>
-      <c r="C24" s="21" t="str">
+      <c r="C24" s="19" t="str">
         <v>Manager: Oh please, don't try that cute routine on me.
 Manager: I've seen every trick in the book.
 Manager: Hit the books tonight, or next time I'm shipping you off to Planet Dummy.</v>
       </c>
-      <c r="D24" s="21">
+      <c r="D24" s="19">
         <v>15</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="20"/>
-      <c r="B25" s="21">
+      <c r="A25" s="18"/>
+      <c r="B25" s="19">
         <v>15</v>
       </c>
-      <c r="C25" s="20" t="str">
+      <c r="C25" s="18" t="str">
         <v>Manager: Alright, that's enough for today.
 Manager: No matter what kind of work you do, remember to eat well, stay hydrated, and leave work on time.
 Managerz:See you tomorrow！ Ciao~</v>
       </c>
-      <c r="D25" s="20"/>
+      <c r="D25" s="18"/>
     </row>
     <row r="26">
-      <c r="A26" s="22" t="str">
-        <v>Performance 3 ending</v>
-      </c>
-      <c r="B26" s="18"/>
-      <c r="C26" s="18"/>
-      <c r="D26" s="18"/>
-      <c r="E26" s="18"/>
-      <c r="F26" s="18"/>
-      <c r="G26" s="18"/>
-      <c r="H26" s="18"/>
-      <c r="I26" s="18"/>
-      <c r="J26" s="18"/>
-      <c r="K26" s="18"/>
-      <c r="L26" s="18"/>
-      <c r="M26" s="18"/>
-      <c r="N26" s="18"/>
-      <c r="O26" s="18"/>
-      <c r="P26" s="18"/>
-      <c r="Q26" s="18"/>
-      <c r="R26" s="18"/>
-      <c r="S26" s="18"/>
-      <c r="T26" s="18"/>
-      <c r="U26" s="18"/>
+      <c r="A26" s="21" t="str" xml:space="preserve">
+        <v>Performance 4 </v>
+      </c>
+      <c r="B26" s="20"/>
+      <c r="C26" s="20"/>
+      <c r="D26" s="20"/>
+      <c r="E26" s="20"/>
+      <c r="F26" s="20"/>
+      <c r="G26" s="20"/>
+      <c r="H26" s="20"/>
+      <c r="I26" s="20"/>
+      <c r="J26" s="20"/>
+      <c r="K26" s="20"/>
+      <c r="L26" s="20"/>
+      <c r="M26" s="20"/>
+      <c r="N26" s="20"/>
+      <c r="O26" s="20"/>
+      <c r="P26" s="20"/>
+      <c r="Q26" s="20"/>
+      <c r="R26" s="20"/>
+      <c r="S26" s="20"/>
+      <c r="T26" s="20"/>
+      <c r="U26" s="20"/>
     </row>
     <row r="27">
-      <c r="A27" s="24"/>
-      <c r="B27" s="24"/>
-      <c r="C27" s="24" t="str">
+      <c r="A27" s="23"/>
+      <c r="B27" s="23">
+        <v>21</v>
+      </c>
+      <c r="C27" s="23" t="str">
         <v>Null：Oops! You haven't checked all the parts yet~</v>
       </c>
-      <c r="D27" s="24"/>
+      <c r="D27" s="23"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="21" t="str" xml:space="preserve">
+        <v>Performance 5 </v>
+      </c>
+      <c r="B28" s="20"/>
+      <c r="C28" s="20"/>
+      <c r="D28" s="20"/>
+      <c r="E28" s="20"/>
+      <c r="F28" s="20"/>
+      <c r="G28" s="20"/>
+      <c r="H28" s="20"/>
+      <c r="I28" s="20"/>
+      <c r="J28" s="20"/>
+      <c r="K28" s="20"/>
+      <c r="L28" s="20"/>
+      <c r="M28" s="20"/>
+      <c r="N28" s="20"/>
+      <c r="O28" s="20"/>
+      <c r="P28" s="20"/>
+      <c r="Q28" s="20"/>
+      <c r="R28" s="20"/>
+      <c r="S28" s="20"/>
+      <c r="T28" s="20"/>
+      <c r="U28" s="20"/>
+    </row>
+    <row customHeight="true" ht="19" r="29">
+      <c r="B29" s="2">
+        <v>22</v>
+      </c>
+      <c r="C29" s="2" t="str">
+        <v>Null：DIRECTOR</v>
+      </c>
+      <c r="D29" s="2"/>
+    </row>
+    <row r="30">
+      <c r="B30" s="2">
+        <v>23</v>
+      </c>
+      <c r="C30" s="2" t="str">
+        <v>Null：SleepyAppleKitty</v>
+      </c>
+      <c r="D30" s="2"/>
+    </row>
+    <row r="31">
+      <c r="B31" s="2">
+        <v>24</v>
+      </c>
+      <c r="C31" s="2" t="str">
+        <v>Null：biba2012</v>
+      </c>
+      <c r="D31" s="2"/>
+    </row>
+    <row r="32">
+      <c r="B32" s="2">
+        <v>25</v>
+      </c>
+      <c r="C32" s="2" t="str">
+        <v>Null：AOI</v>
+      </c>
+      <c r="D32" s="2"/>
+    </row>
+    <row r="33">
+      <c r="B33" s="2">
+        <v>26</v>
+      </c>
+      <c r="C33" s="2" t="str">
+        <v>Null：Yi geng</v>
+      </c>
+      <c r="D33" s="2"/>
+    </row>
+    <row r="34">
+      <c r="B34" s="2">
+        <v>27</v>
+      </c>
+      <c r="C34" s="2" t="str">
+        <v>Null：Nino</v>
+      </c>
+      <c r="D34" s="2"/>
+    </row>
+    <row r="35">
+      <c r="B35" s="2">
+        <v>28</v>
+      </c>
+      <c r="C35" s="2" t="str">
+        <v>Null：Xing Ren</v>
+      </c>
     </row>
   </sheetData>
 </worksheet>
